--- a/output/full_scan/batch_seq2_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq2_2026-10-22.xlsx
@@ -444,7 +444,7 @@
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.01152125848672</v>
+        <v>72.01152128381725</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>36.97312949644594</v>
+        <v>36.97312965608842</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>5.636025976617844</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1913420545571699</v>
+        <v>0.1913420545052558</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>87.2445624022364</v>
+        <v>87.24456239433516</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>53.62495552070135</v>
+        <v>53.62495541844681</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.482726485597089</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.8166764678159333</v>
+        <v>0.8166764682052889</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.37825767787456</v>
+        <v>66.37825775986849</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.37331874046029</v>
+        <v>33.37331902938807</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.121547089493213</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.05824093128824015</v>
+        <v>-0.05824093139206743</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>978.5079953320959</v>
+        <v>978.5079953320957</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>93.2</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.8864819328559</v>
+        <v>68.88648203316824</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>42.44150035458762</v>
+        <v>42.44150054449345</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.291744269371122</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4728042986854355</v>
+        <v>0.4728042981922354</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.18160923182391</v>
+        <v>61.18160926675926</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22.06221631850352</v>
+        <v>22.06221627988486</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>5.49373864515799</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.01444191134117245</v>
+        <v>0.01444191125032018</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.98619257512979</v>
+        <v>61.98619290243865</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>27.15708865956734</v>
+        <v>27.15708878009825</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.8469311963211047</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.8258859043511939</v>
+        <v>0.8258859022746101</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>61.7633008343836</v>
+        <v>61.76330080081663</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33.41782074996622</v>
+        <v>33.4178208210438</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.160238568251936</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.06356760770168102</v>
+        <v>0.06356760766274779</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>58.76239797321045</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.59333444184112</v>
+        <v>14.59333450303726</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>2.14542212383939</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.008803846069264914</v>
+        <v>0.008803846056288318</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>939.2120612408212</v>
+        <v>939.2120612408211</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>50.6</v>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>62.21882371209196</v>
+        <v>62.21882386180707</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>31.49038742975834</v>
+        <v>31.49038758542867</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.227990776135795</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2284785766093103</v>
+        <v>0.2284785763627134</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.81324851254448</v>
+        <v>64.81324855473989</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>37.7220250288298</v>
+        <v>37.72202506519466</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.219956408623487</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.126513013315223</v>
+        <v>0.1265130133282014</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>862.6390992617412</v>
+        <v>862.6390992617413</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>53.6</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>72.48000171407539</v>
+        <v>72.48000145355144</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33.75083671446039</v>
+        <v>33.75083676230297</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>5.905504304893155</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.5441570614852498</v>
+        <v>0.5441570613295028</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>836.850454741478</v>
+        <v>836.8504547414778</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>67.8</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>59.5044255357663</v>
+        <v>59.50442554972993</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14.78225697776555</v>
+        <v>14.7822569724705</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.7260814030032949</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.03318708827204175</v>
+        <v>0.03318708806438575</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>830.5391081270916</v>
+        <v>830.5391081270917</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>32.45</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.98125431765103</v>
+        <v>57.98125435147196</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15.56253808893555</v>
+        <v>15.56253826387973</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.441759146664404</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.09533824194375451</v>
+        <v>0.09533824181396777</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>81.06958699301771</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>60.39163057299924</v>
+        <v>60.39163056405715</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.054767956119938</v>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>820.28382879643</v>
+        <v>820.2838287964305</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>47</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.84545847995338</v>
+        <v>59.84545847157158</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.29984273407921</v>
+        <v>22.29984277700484</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2.168957906239822</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1172801234226131</v>
+        <v>0.1172801233317518</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.6630897164402</v>
+        <v>56.66308975437022</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.69961370493801</v>
+        <v>31.6996137967266</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.750187145687303</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.253220864161877</v>
+        <v>1.25322086231892</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>809.9146853372496</v>
+        <v>809.9146853372497</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>11.65</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.87028633940506</v>
+        <v>60.8702864890967</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31.06700668304604</v>
+        <v>31.0670070564492</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.9634403283350106</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.06504436926269813</v>
+        <v>0.06504436918031667</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.32165205432308</v>
+        <v>51.32165219627097</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.25612667166157</v>
+        <v>28.25612691051505</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.760879485801488</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.03523733262348444</v>
+        <v>0.03523733238986909</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.69674015885195</v>
+        <v>55.69674014301808</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>28.30654556309412</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.700372715809111</v>
+        <v>1.700372717885653</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>54.85463723019171</v>
+        <v>54.8546372662521</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.47213853193483</v>
+        <v>31.4721385808865</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.4455587567304397</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.2741134751507721</v>
+        <v>-0.274113475215666</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.21071010285733</v>
+        <v>50.2107102198561</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16.13755008036714</v>
+        <v>16.13755016667206</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.962348391481295</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1758350868684928</v>
+        <v>0.1758350864791316</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>60.55226801661612</v>
+        <v>60.55226802869725</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>30.46580631447965</v>
+        <v>30.46580656351762</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>2.943431122394263</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.48803488087124</v>
+        <v>0.4880348799887002</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>767.4879204168825</v>
+        <v>767.4879204168826</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>29.4</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>53.88409781058649</v>
+        <v>53.88409830639194</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.3465892534475</v>
+        <v>20.3465895115729</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>1.182865639882094</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.03181298729491594</v>
+        <v>0.03181298678003004</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>54.70273955792547</v>
+        <v>54.70273956364665</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>33.87696006331693</v>
+        <v>33.87696016817376</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>2.200009827261391</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.1859337244668182</v>
+        <v>-0.1859337245966008</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>44.16082210659339</v>
+        <v>44.16082212943967</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15.87637321141903</v>
+        <v>15.87637359377039</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.732198741499918</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-63.25340762700892</v>
+        <v>-63.25340764388201</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.57794359067077</v>
+        <v>49.57794359717469</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>30.36006907825238</v>
+        <v>30.36006910038712</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.7828541872483388</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.9164691083737837</v>
+        <v>-0.9164691083867624</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.87779669487198</v>
+        <v>55.87779665890348</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.90227297789972</v>
+        <v>26.90227291402267</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.38751345532831</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.01162391851396608</v>
+        <v>-0.01162391852694564</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>737.0709026497335</v>
+        <v>737.0709026497364</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>44.95</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.28752471568576</v>
+        <v>54.28752470552211</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>31.98403809396659</v>
+        <v>31.98403810325876</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.9871419424109069</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.06599900979774409</v>
+        <v>0.06599900977178796</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>733.4053455155348</v>
+        <v>733.4053455155349</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>32</v>
@@ -2039,7 +2039,7 @@
         <v>64.6486820334523</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.87613739274893</v>
+        <v>27.87613744975975</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.8637118404807616</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1833789077667745</v>
+        <v>0.1833789077278383</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.75091478070146</v>
+        <v>51.75091488385754</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.44810949508281</v>
+        <v>16.4481097510965</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.9106424168101875</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2210650450568236</v>
+        <v>0.2210650448361944</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>712.7658550622134</v>
+        <v>712.7658550622149</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>60.5</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.41761547269045</v>
+        <v>51.41761546427496</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>27.80263509089112</v>
+        <v>27.80263524025635</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.8988394129954463</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4915053935323512</v>
+        <v>0.4915053934674587</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.11558962605974</v>
+        <v>51.11558967366371</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24.14116007936316</v>
+        <v>24.14116027052971</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>1.367489313772294</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1423110843843965</v>
+        <v>0.1423110842675868</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>70.58901047887511</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>53.61155815813269</v>
+        <v>53.61155817241053</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1.130774262600237</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1082664549160642</v>
+        <v>0.1082664549290412</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>65.37325282214809</v>
+        <v>65.37325280218914</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>29.72074056658415</v>
+        <v>29.72074055577313</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.025606667386425</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.9048303256427364</v>
+        <v>-0.9048303255908152</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>695.2851948727273</v>
+        <v>695.2851948727274</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>99.3</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>60.33236208528528</v>
+        <v>60.33236227271571</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46.24346623453943</v>
+        <v>46.24346692963582</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.83997571841871</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.112738557288881</v>
+        <v>-0.1127385583271772</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>68.42758917958174</v>
+        <v>68.42758922581473</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>35.65782084276384</v>
+        <v>35.65782097509138</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.8931984883673666</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.07237469662931639</v>
+        <v>0.07237469660335999</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.8311240617797</v>
+        <v>47.8311240397087</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.34318188142335</v>
+        <v>37.34318189921417</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.508621970714119</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.1507637795828307</v>
+        <v>-0.1507637795698498</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.49290210592657</v>
+        <v>52.49290210859566</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>34.99943242326281</v>
+        <v>34.99943255978155</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.5659887137495955</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.4265559720162033</v>
+        <v>-0.4265559720940755</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>667.2038570154872</v>
+        <v>667.2038570154873</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>23.1</v>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.56022345363913</v>
+        <v>58.56022367043749</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.96076769717818</v>
+        <v>20.96076794198</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.8160339894195259</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.05540469870659431</v>
+        <v>0.05540469857680347</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.05761313838978</v>
+        <v>48.05761320208011</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>34.89878867825588</v>
+        <v>34.89878876278864</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.6957602134886265</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.4157986622578123</v>
+        <v>-0.4157986626601468</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.84656207991704</v>
+        <v>51.84656204876762</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.13282875617449</v>
+        <v>18.1328288059734</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.7303460114355046</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.4228739135383557</v>
+        <v>0.4228739145766496</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46.6308586179766</v>
+        <v>46.63085865399727</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29.1947458011621</v>
+        <v>29.19474597372984</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.7748970947860256</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-10.55767330735352</v>
+        <v>-10.55767331994282</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>646.5069385341948</v>
+        <v>646.5069385341952</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>31.45</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.38621303165881</v>
+        <v>56.38621300565264</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.98378583062591</v>
+        <v>21.98378591479959</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.7383573143368219</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0214275377635072</v>
+        <v>0.02142753769861631</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>626.5073836921173</v>
+        <v>626.5073836921174</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>79.40000000000001</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.30985533615802</v>
+        <v>50.30985543113707</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.25622081935166</v>
+        <v>22.25622077568508</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.7729220504468551</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2000685326677423</v>
+        <v>0.2000685318890202</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>617.3254907825433</v>
+        <v>617.3254907825431</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>65.8</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.73086199930737</v>
+        <v>56.73086208455761</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.26293557636498</v>
+        <v>16.26293565680193</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.5811173776953098</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.08212362729519723</v>
+        <v>0.08212362698370712</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>44.70157140631628</v>
+        <v>44.70157145801519</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.63569431685503</v>
+        <v>16.63569453295286</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.7727158534581907</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.6039119310331342</v>
+        <v>-0.6039119327204077</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>613.51274753204</v>
+        <v>613.5127475320402</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>74</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.12952039878449</v>
+        <v>51.12952026089461</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>29.36745163835712</v>
+        <v>29.36745150378813</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.5735088920435083</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.06711902041535556</v>
+        <v>-0.06711901989621083</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.91218030910109</v>
+        <v>44.91218033326587</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>26.62838229721726</v>
+        <v>26.62838227876462</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.3977578603644275</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.2171792797079298</v>
+        <v>-0.2171792802011199</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.32303854895721</v>
+        <v>47.32303863429754</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>9.161953906483351</v>
+        <v>9.161953961365315</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.6450825324256385</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.2198283348440511</v>
+        <v>-0.2198283361419147</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.62229150995402</v>
+        <v>46.62229152080832</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20.46221990893441</v>
+        <v>20.46222010625021</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.4418527200123052</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.6301830414637507</v>
+        <v>-0.6301830416454673</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.07575774199096</v>
+        <v>44.07575777308143</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.64129120361435</v>
+        <v>20.64129135645552</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.264012772908557</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.509757840753681</v>
+        <v>-1.50975784212942</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.7303378714841</v>
+        <v>51.73033791792935</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.6839792976612</v>
+        <v>24.68397939377476</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.3423168728970312</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.05828282056824657</v>
+        <v>-0.05828282063313872</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.80039757952178</v>
+        <v>49.80039762489012</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>42.40923417107147</v>
+        <v>42.40923417830059</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.5576037116275411</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1244007262291466</v>
+        <v>-0.12440072629404</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>59.95827445008423</v>
+        <v>59.95827446712548</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>37.00015006703994</v>
+        <v>37.00015005278764</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>1.084337245314478</v>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>591.4928400487121</v>
+        <v>591.4928400487122</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>63.4</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.17672307658722</v>
+        <v>50.17672299567712</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.39938159551257</v>
+        <v>22.39938157328661</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.4497034798590612</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1455220979954942</v>
+        <v>-0.1455220975801833</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.15400771937836</v>
+        <v>54.15400753601283</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.53230266518854</v>
+        <v>26.53230278411035</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>1.920458338773163</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.05792086662189377</v>
+        <v>-0.05792086660891496</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>56.11535900778325</v>
+        <v>56.11535908013342</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>38.44035962430295</v>
+        <v>38.44035978620812</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.5444527600209411</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.03189287764489512</v>
+        <v>-0.03189287768382981</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>583.6218493372835</v>
+        <v>583.6218493372834</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>37</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45.42817077932158</v>
+        <v>45.42817077191017</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.32023209553492</v>
+        <v>22.32023233048425</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4470308669276036</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.2603695860182671</v>
+        <v>-0.2603695860961381</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>54.47082250909204</v>
+        <v>54.47082252276194</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>31.3460183995708</v>
+        <v>31.34601849591558</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.5038978563807209</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1132678104675628</v>
+        <v>0.1132678104156495</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>567.2261334110034</v>
+        <v>567.2261334110013</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>30.55</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46.99577668261471</v>
+        <v>46.99577681056817</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>60.96233901180326</v>
+        <v>60.96233897916145</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.7322735536804811</v>
@@ -3718,7 +3718,7 @@
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>564.5326063490805</v>
+        <v>564.5326063490808</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>50.7</v>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>63.94336910278513</v>
+        <v>63.94336931783591</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>38.15514308886554</v>
+        <v>38.15514316363071</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.536237710032485</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.4917566876893802</v>
+        <v>0.4917566868717267</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>558.3921197980416</v>
+        <v>558.3921197980411</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>33.15</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.5450933310661</v>
+        <v>49.5450933118106</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>26.48341676195001</v>
+        <v>26.48341674678545</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.855381171753604</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.02456174718742918</v>
+        <v>-0.02456174722636692</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.85041647240433</v>
+        <v>52.85041667766748</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>23.6855880258723</v>
+        <v>23.68558809985667</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.5629531268076031</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.04430804774262395</v>
+        <v>0.04430804756092332</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.58336487876723</v>
+        <v>54.5833650362486</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.43520693394841</v>
+        <v>12.43520698023605</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.5212972976237145</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.04994472273218917</v>
+        <v>0.0499447224985777</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.56092936297882</v>
+        <v>46.56092933366212</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>41.15910307328225</v>
+        <v>41.15910308025366</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.3098762123545035</v>
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>549.3090398973353</v>
+        <v>549.3090398973355</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>56.5</v>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>57.56116278695737</v>
+        <v>57.56116279392726</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>53.53133450625072</v>
+        <v>53.53133447365472</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.6880925206509628</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.383880738888823</v>
+        <v>-0.383880738564351</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>33.2636754686758</v>
+        <v>33.26367547200719</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.48884235185984</v>
+        <v>22.48884234029382</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.7055749475968663</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-148.6354741838039</v>
+        <v>-148.6354741993787</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>56.30046714114538</v>
+        <v>56.30046725608516</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.65216906611114</v>
+        <v>13.65216924506242</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1.154782751603843</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.01305840182157174</v>
+        <v>0.01305840175667883</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>54.43068037579933</v>
+        <v>54.43068039805571</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.47696044231118</v>
+        <v>16.47696056735744</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.7000791229251062</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.09630391940233496</v>
+        <v>0.09630391929850438</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.29664971400784</v>
+        <v>44.29664978617273</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14.25953474765673</v>
+        <v>14.25953497275385</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.672378374143566</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.83153001010417</v>
+        <v>-1.83153001282972</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.78337699994026</v>
+        <v>50.78337696804693</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.62417415970189</v>
+        <v>20.62417413962514</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.5834968729702051</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1494235411585097</v>
+        <v>0.1494235411807477</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>40.83385401513208</v>
+        <v>40.83385381717951</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23.55428440418983</v>
+        <v>23.55428445845613</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.3036153438054449</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-22.92220494392996</v>
+        <v>-22.92220494782335</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>53.21163981928802</v>
+        <v>53.21163987147064</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.16876082682215</v>
+        <v>16.16876092499805</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.7506520411068461</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.01735493926841446</v>
+        <v>-0.01735493933330993</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>55.443841944296</v>
+        <v>55.44384195100353</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>39.54960883966648</v>
+        <v>39.54960903625241</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.6098231876927032</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.188501417225448</v>
+        <v>-1.188501417290341</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.13948376180296</v>
+        <v>47.13948377023222</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>44.55110318646435</v>
+        <v>44.55110336452399</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.486064468593901</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.166031766397474</v>
+        <v>-2.166031766475342</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.47233599267587</v>
+        <v>50.47233613455456</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>56.91558592657974</v>
+        <v>56.91558600459078</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.575801946174918</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.04835275842668801</v>
+        <v>-0.04835275843966591</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>505.9373801742298</v>
+        <v>505.9373801742294</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>30.5</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>56.20738109064264</v>
+        <v>56.20738100147804</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.98203731472652</v>
+        <v>18.98203736871284</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>2.741423071238442</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.07417081464048159</v>
+        <v>-0.07417081462750377</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.96916604316861</v>
+        <v>51.9691660597827</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.17647718984396</v>
+        <v>17.17647729732905</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.6757950658167228</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0146725699506111</v>
+        <v>0.01467256992465439</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>501.1669593730269</v>
+        <v>501.1669593730268</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>44.8</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>54.20940990342764</v>
+        <v>54.20941003294092</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>38.03621085346469</v>
+        <v>38.03621085728004</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.4699885038300045</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.08679133108109455</v>
+        <v>0.08679133084748014</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.85022667876883</v>
+        <v>48.85022684211369</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>22.87358135816736</v>
+        <v>22.87358162888154</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.5743380799575032</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1193404709833794</v>
+        <v>-0.1193404712299771</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.84674747990102</v>
+        <v>48.84674749294749</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.14637898310014</v>
+        <v>16.14637911283667</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.4886890856759769</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.4258643229708181</v>
+        <v>-0.4258643230357048</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>38.32230277548602</v>
+        <v>38.32230278431655</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.92527773441358</v>
+        <v>22.92527774712975</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.4464089368305957</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.6858066147326772</v>
+        <v>-0.6858066148235286</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.99037878304477</v>
+        <v>52.99037879680964</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>37.72164842639335</v>
+        <v>37.72164858334081</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.5136415914373952</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.6167445953589601</v>
+        <v>-0.616744595501721</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>47.68236866641091</v>
+        <v>47.68236875012133</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.81555674749276</v>
+        <v>18.81555682872665</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.3874886152781585</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.07600583110223663</v>
+        <v>-0.0760058311801082</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.7290960195535</v>
+        <v>45.72909610946633</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.41975996927152</v>
+        <v>15.4197599767136</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.5881016056062572</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1257958077406859</v>
+        <v>-0.1257958080132409</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.05709866781418</v>
+        <v>51.0570987734384</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>37.30629724925645</v>
+        <v>37.30629773350044</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.4386498455795602</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.02430973624925645</v>
+        <v>-0.02430973640500289</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.87719465905667</v>
+        <v>51.87719466575076</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>29.72677835872028</v>
+        <v>29.72677848806405</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.5011552354874401</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.08123785938093764</v>
+        <v>-0.08123785939651185</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.33793600590892</v>
+        <v>48.33793599299686</v>
       </c>
       <c r="I89" s="2" t="n">
         <v>34.6118466920385</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.05159290608492229</v>
+        <v>-0.05159290605896566</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.80163498628143</v>
+        <v>43.80163518359259</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>30.21849602388081</v>
+        <v>30.21849597717921</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.167602265069588</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2203852932927231</v>
+        <v>0.2203852930331489</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>54.17730298139352</v>
+        <v>54.177303046787</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>26.20762962545895</v>
+        <v>26.20762963501019</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.8698553255406335</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.04242767090736523</v>
+        <v>0.04242767088141122</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.17568107488231</v>
+        <v>42.17568105404067</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.62963158632832</v>
+        <v>21.62963167158804</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.3074233721273395</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-2.15347367328512</v>
+        <v>-2.153473673362985</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.07994188514705</v>
+        <v>49.0799419243948</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>44.38768991280249</v>
+        <v>44.38769004569455</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.715034821669062</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.6284025620364364</v>
+        <v>-0.6284025622311211</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>55.16008919018346</v>
+        <v>55.1600892133005</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.24904696682595</v>
+        <v>16.24904693598768</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.7880518068979494</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.06432485330160688</v>
+        <v>0.06432485326266753</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>437.8963433719769</v>
+        <v>437.896343371977</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>28.25</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45.06190775757143</v>
+        <v>45.06190774836685</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.22275712303044</v>
+        <v>15.22275724870133</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.1811770112229872</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.02881370803150238</v>
+        <v>0.02881370800554478</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>33.77596681795559</v>
+        <v>33.77596683612839</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.21008100546875</v>
+        <v>20.21008121233188</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.8719064807750735</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-38.9895222320163</v>
+        <v>-38.98952223798647</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>24.03413484838599</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>38.88077589186383</v>
+        <v>38.88078230682346</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>4.024376545896833</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.09872636719862604</v>
+        <v>0.09872439778424713</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>435.2528833623946</v>
+        <v>435.2528833623944</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>57.3</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.10454484073136</v>
+        <v>46.10454507009941</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>28.2620975992715</v>
+        <v>28.26209764489364</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.7805558426368758</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.3069868403966032</v>
+        <v>-0.3069868415387287</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.56172970001309</v>
+        <v>51.56172967278525</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>35.02520158795119</v>
+        <v>35.02520162455451</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.3106206944549773</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.23118500950891</v>
+        <v>41.23118453685744</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.84855182434318</v>
+        <v>11.84855182149285</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.7776832763664637</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1689579676520655</v>
+        <v>-0.1689579675222656</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>51.88894886834126</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.10429738661472</v>
+        <v>17.1042974157168</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.457145239940278</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1182300722915781</v>
+        <v>-0.1182300723175367</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>37.80757261178363</v>
+        <v>37.80757258327821</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>20.06587423189432</v>
+        <v>20.06587438544054</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>1.092061727717139</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-18.44774036324672</v>
+        <v>-18.44774036194905</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>38.3698318978108</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>23.54669701544917</v>
+        <v>23.54669705799797</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.4344532034917649</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.3890001846001246</v>
+        <v>-0.3890001846130985</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.425569712571</v>
+        <v>49.42556968204831</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.34332668120647</v>
+        <v>13.34332670588721</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.8986742550231747</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.02516306226863707</v>
+        <v>0.02516306229459622</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>50.10806605653558</v>
+        <v>50.10806586859859</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.23999612676874</v>
+        <v>14.23999617639458</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.7494444373144629</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1324530423458904</v>
+        <v>0.1324530425795026</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>412.6468741318902</v>
+        <v>412.6468741318903</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>1980</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.79667245243727</v>
+        <v>39.7966724681844</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.64278065586766</v>
+        <v>15.64278077351065</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.835728833314724</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-37.96644098735837</v>
+        <v>-37.96644099306841</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>411.9205697005821</v>
+        <v>411.9205697005818</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>154.5</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.04310384879723</v>
+        <v>40.04310383576986</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.513926907668</v>
+        <v>14.51392691747885</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.6622104319679991</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-2.015451016779252</v>
+        <v>-2.015451016623527</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.98079929522113</v>
+        <v>43.98079928636888</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>33.92675236620291</v>
+        <v>33.92675243413379</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.4142592357494622</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.5354356148967725</v>
+        <v>-0.5354356149486874</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>407.5655515414896</v>
+        <v>407.5655515414895</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>39.7</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>31.39583481464607</v>
+        <v>31.3958348981362</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>32.37754964536087</v>
+        <v>32.37754972434309</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.5937912816083324</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0191610495941541</v>
+        <v>0.01916104943841046</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>405.9653358802241</v>
+        <v>405.965335880224</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>41.55</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>53.58921131331068</v>
+        <v>53.5892113825202</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.28089381936037</v>
+        <v>13.28089397835849</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>1.106363939837911</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.02076223507088835</v>
+        <v>0.02076223503195496</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.58645451189201</v>
+        <v>46.58645417038232</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>22.64206671947449</v>
+        <v>22.64206677084688</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.6722876356748286</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1705990414969761</v>
+        <v>0.1705990414450657</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45.05969154622352</v>
+        <v>45.05969159488107</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.18122837576256</v>
+        <v>19.18122852191815</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>1.200305590745833</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-4.458245444610007</v>
+        <v>-4.458245447984449</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>397.3458914834484</v>
+        <v>397.3458914834493</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>17.25</v>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.86068501591137</v>
+        <v>35.86068437317296</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>40.9981907490691</v>
+        <v>40.9981915134596</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.59214655751045</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.05352756653121979</v>
+        <v>-0.05352756634951789</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.02974689301811</v>
+        <v>40.02974694136984</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.15466313623677</v>
+        <v>20.15466335449518</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.8273680744464309</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-2.708792090762915</v>
+        <v>-2.708792092450175</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>41.54640848180976</v>
+        <v>41.54640854208773</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.83487392949933</v>
+        <v>19.83487393168418</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>1.736104627937512</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.06396358938839242</v>
+        <v>-0.06396358944030472</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.80598849628227</v>
+        <v>44.80598865555593</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>5.723190740646361</v>
+        <v>5.723190909352819</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.7346377442266808</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.01015735790188003</v>
+        <v>-0.01015735791485808</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>27.65934304168219</v>
+        <v>27.65934311608689</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>25.58184057446929</v>
+        <v>25.58184084445951</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.9021606381539965</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.2095421676142792</v>
+        <v>-0.2095421679387447</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>388.3665423841368</v>
+        <v>388.3665423841375</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>414</v>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>33.69826424651312</v>
+        <v>33.69826424409574</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>21.60311235909639</v>
+        <v>21.60311240505059</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.7034620968874117</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-10.93307122195312</v>
+        <v>-10.93307122201802</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>388.0599836370024</v>
+        <v>388.0599836370025</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>28.7</v>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>45.68698931075303</v>
+        <v>45.68698924161206</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>23.39729926931367</v>
+        <v>23.39729930574676</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.7144441596936296</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.04309037884797089</v>
+        <v>-0.04309037879605493</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>48.66369954736601</v>
+        <v>48.66369955868458</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>41.23398734800613</v>
+        <v>41.23398732997928</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>1.194863568448148</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>47.88810072361709</v>
+        <v>47.88810082903944</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.59641018444358</v>
+        <v>18.59641015228948</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>1.28196601692693</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.02860764549130367</v>
+        <v>0.02860764550428264</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>385.3762654603358</v>
+        <v>385.376265460336</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>165</v>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.7752532705931</v>
+        <v>45.77525276696832</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>25.44304048047915</v>
+        <v>25.44304081025736</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>0.785629236691521</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-1.25132875190409</v>
+        <v>-1.25132874827006</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>384.7607867906028</v>
+        <v>384.7607867906029</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>150</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>38.44490702248425</v>
+        <v>38.4449070777007</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>20.03654593064958</v>
+        <v>20.03654605196363</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>1.082218677928881</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-2.127794904595318</v>
+        <v>-2.127794906542099</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>40.57030253736148</v>
+        <v>40.57030253338733</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>25.22117580280062</v>
+        <v>25.2211759003664</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.1830506540752569</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-1.021371257975888</v>
+        <v>-1.021371258053758</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46.45378032805419</v>
+        <v>46.45378039543859</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>20.91367864691717</v>
+        <v>20.91367871709222</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.6455668080909884</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.007783502751850908</v>
+        <v>-0.007783502770021375</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>378.4511940790474</v>
+        <v>378.4511940790469</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>17.8</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>33.44025756447199</v>
+        <v>33.44025785806591</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>25.32554531127773</v>
+        <v>25.32554532996899</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>1.496141996711587</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.01682013510705266</v>
+        <v>0.0168201348993938</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>376.1703350512394</v>
+        <v>376.1703350512393</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>10.1</v>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>48.48806652853281</v>
+        <v>48.48806664457013</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>17.94007971343402</v>
+        <v>17.94007986237215</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>1.00592323465078</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.003141606783280008</v>
+        <v>0.003141606770301689</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>374.3240104449598</v>
+        <v>374.3240104449597</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>9.69</v>
@@ -7233,7 +7233,7 @@
         <v>48.33578463111722</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>14.20594726057299</v>
+        <v>14.20594720650877</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>1.48755947772858</v>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>373.065054831433</v>
+        <v>373.0650548314325</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>44.95</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>50.23435028262487</v>
+        <v>50.23435030714446</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>31.26413344665607</v>
+        <v>31.26413344224337</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.9091880319532467</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.1080608886988853</v>
+        <v>-0.1080608890882491</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>23.17452352348832</v>
+        <v>23.1745235605693</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>37.40535049877278</v>
+        <v>37.40535048512301</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>1.551192223326863</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.08748139932545751</v>
+        <v>-0.08748139945524569</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>369.8945577536688</v>
+        <v>369.8945577536689</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>22.6</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>48.40562553173388</v>
+        <v>48.40562540382759</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>17.60929467587597</v>
+        <v>17.60929475770435</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>1.37652197500104</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.05235255373088216</v>
+        <v>-0.05235255364003338</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>33.29238003766019</v>
+        <v>33.29238003694897</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>20.01417016753966</v>
+        <v>20.01417023013257</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.9772696762944962</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-1.458584842041523</v>
+        <v>-1.458584842080443</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>30.83847973121851</v>
+        <v>30.83847979631722</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>26.3662449779921</v>
+        <v>26.36624517289241</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.6282760169832019</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.07242840570242964</v>
+        <v>-0.07242840597498298</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>353.4146288081824</v>
+        <v>353.4146288081522</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>12.65</v>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>47.95727688960102</v>
+        <v>47.95727691222131</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>6.056717282562675</v>
+        <v>6.056717271925147</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>1.026169918215531</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.03012203631716596</v>
+        <v>-0.0301220363561039</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>351.5687460295064</v>
+        <v>351.5687460295065</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>10</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>47.66679103693937</v>
+        <v>47.66679111497716</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>13.63532228813065</v>
+        <v>13.63532225352751</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.5514827953515301</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.00161071103796142</v>
+        <v>-0.001610711115834031</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>42.79420083393509</v>
+        <v>42.79420096286727</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>12.0740024093368</v>
+        <v>12.07400251860253</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.4959012731108359</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.1204959360241259</v>
+        <v>-0.1204959363615772</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>348.9422908625988</v>
+        <v>348.9422908625989</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>38.5</v>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>43.21014048185595</v>
+        <v>43.21014051536695</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>25.37721213498097</v>
+        <v>25.37721211890972</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.4887912607820229</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.1394412346547917</v>
+        <v>-0.1394412347067054</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>348.8941405443042</v>
+        <v>348.8941405443043</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>52.6</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>40.75299843264013</v>
+        <v>40.75299843695109</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>21.77948093349397</v>
+        <v>21.77948113686539</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.3518106111886002</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.7875726059359345</v>
+        <v>-0.7875726062993356</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>5.069932061482149</v>
+        <v>5.069932061131354</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>22.14607556650968</v>
+        <v>22.14607552692666</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>7.507704782032561e-05</v>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>38.90210359204661</v>
+        <v>38.90210361039235</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>19.0966603348498</v>
+        <v>19.09666043325018</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.4674163989451693</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-2.331580700693181</v>
+        <v>-2.331580701212329</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>343.7186144757105</v>
+        <v>343.7186144757103</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>7</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>52.24883278768943</v>
+        <v>52.24883304470157</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>15.46697564066635</v>
+        <v>15.46697571560827</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.9150693411207079</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.01192428108806061</v>
+        <v>0.01192428104652935</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>335.5221687409977</v>
+        <v>335.5221687409956</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>26.65</v>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>38.76512554833096</v>
+        <v>38.76512523659039</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>17.78844455875409</v>
+        <v>17.78844487042035</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0.6885351780687545</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.03179534818105301</v>
+        <v>-0.03179534806424422</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>27.25898867953067</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>39.22977623276762</v>
+        <v>39.22977624247041</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.6339276652623533</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.01629111682239892</v>
+        <v>0.01629111680942263</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>45.5312211322231</v>
+        <v>45.53122126855208</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>20.54379971365171</v>
+        <v>20.54379987542599</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.5509319074711697</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.1911985791117952</v>
+        <v>-0.1911985795271106</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>31.80463473533119</v>
+        <v>31.80463475813573</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>28.23726848145673</v>
+        <v>28.23726838890791</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>1.678246372455477</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-1.1701467805158</v>
+        <v>-1.17014678492856</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>35.58920547664816</v>
+        <v>35.5892055010828</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>25.40986784673985</v>
+        <v>25.40986804101697</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.4960621845680346</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-3.821567965001821</v>
+        <v>-3.821567966040165</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>320.8304043657918</v>
+        <v>320.8304043657914</v>
       </c>
       <c r="E147" s="2" t="n">
         <v>14.75</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>41.4930462730711</v>
+        <v>41.4930464919636</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>11.77303492163009</v>
+        <v>11.77303499519886</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.9405185829185964</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-0.01367244385481431</v>
+        <v>-0.01367244401055982</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>43.41128687793822</v>
+        <v>43.41128713736712</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>26.87423962009926</v>
+        <v>26.87423962281596</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.5440602220894665</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>0.04657204046266661</v>
+        <v>0.0465720404107528</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>318.4208986247124</v>
+        <v>318.4208986247122</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>41.95</v>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>41.40578074293858</v>
+        <v>41.40578083171332</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>14.26415938739378</v>
+        <v>14.26415951482016</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.7367818237133354</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-0.2500843336873179</v>
+        <v>-0.2500843339339102</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>40.60512219934121</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>20.64618278020297</v>
+        <v>20.6461827624845</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>0.5193038146236004</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.05668529608284356</v>
+        <v>0.056685296016112</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>41.20583796918302</v>
+        <v>41.20583795825427</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>23.47367057269205</v>
+        <v>23.47367064736804</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.3935347201005882</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-2.144610318870021</v>
+        <v>-2.144610318857026</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>40.03979120623708</v>
+        <v>40.03979126336474</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>15.17821013065401</v>
+        <v>15.1782102206773</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>1.004031322246317</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-1.807213183420013</v>
+        <v>-1.807213184977422</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>32.67242127792825</v>
+        <v>32.67242127514922</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>24.52801474103789</v>
+        <v>24.52801480641778</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0.6060058793669049</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-3.367631158465846</v>
+        <v>-3.367631158400948</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>40.29245755031351</v>
+        <v>40.29245756917551</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>13.84638717384776</v>
+        <v>13.84638721840131</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.6277342822374155</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.272347270201557</v>
+        <v>-0.2723472705389958</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>41.84214304446569</v>
+        <v>41.84214302158428</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>20.28628866963086</v>
+        <v>20.28628866111793</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>1.066510926519209</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.1206406581040812</v>
+        <v>-0.1206406580781273</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>38.96871520574998</v>
+        <v>38.9687151693331</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>21.70926500872058</v>
+        <v>21.70926503157643</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.7409943338236015</v>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>38.47920221453331</v>
+        <v>38.47920223364049</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>19.37511133098672</v>
+        <v>19.37511152472066</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.7114175233726696</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-1.820804624054196</v>
+        <v>-1.820804624287825</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>303.4610374858549</v>
+        <v>303.461037485857</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>63.8</v>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>43.32511210513685</v>
+        <v>43.32511211465981</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>8.53992164724376</v>
+        <v>8.53992162510729</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>1.288662446083401</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>-0.04992135377583018</v>
+        <v>-0.04992135403540721</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>301.1151700796448</v>
+        <v>301.1151700796447</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>51.3</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>37.22424987346584</v>
+        <v>37.22424992718076</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>19.62863937959914</v>
+        <v>19.62863947099991</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.9453115237039595</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.1652062222038171</v>
+        <v>-0.1652062223725366</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>40.63629062540073</v>
+        <v>40.63629050966761</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>17.96483272698014</v>
+        <v>17.96483267782506</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.5891408943200332</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.1085403939981573</v>
+        <v>0.1085403939722038</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>41.63928191182292</v>
+        <v>41.63928100035389</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>28.49316089562965</v>
+        <v>28.49316202735302</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>1.338187363573842</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-0.0901796370607031</v>
+        <v>-0.09017963638581393</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>50.23698855272781</v>
+        <v>50.23698827936907</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>11.72633761077968</v>
+        <v>11.72633758161561</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.9043423997726061</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.004708546302130016</v>
+        <v>0.004708546354044361</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>290.6492853974243</v>
+        <v>290.6492853974241</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>1100</v>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>29.42050794741145</v>
+        <v>29.4205079885552</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>39.330993895055</v>
+        <v>39.33099392281549</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.6426488410063192</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-2.325828051005459</v>
+        <v>-2.325828054120265</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>289.4339090484518</v>
+        <v>289.4339090484513</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>507</v>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>37.5803758719079</v>
+        <v>37.58037588131209</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>15.93739540776461</v>
+        <v>15.93739553750019</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.9196563424994382</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-11.25119901376995</v>
+        <v>-11.25119901493813</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>44.70286645016066</v>
+        <v>44.70286701232482</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>19.23220931469652</v>
+        <v>19.23220938709574</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.7543890734031765</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.0737541963253411</v>
+        <v>-0.07375419677959141</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>284.2446359220839</v>
+        <v>284.2446359220837</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>59.2</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>42.8505188344043</v>
+        <v>42.85051880141275</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>11.13661471121562</v>
+        <v>11.13661471387521</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0.2063736436092274</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.1722945710638379</v>
+        <v>-0.1722945710248983</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>284.116616182696</v>
+        <v>284.1166161826961</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>124</v>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>39.07110034888377</v>
+        <v>39.0711004518755</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>28.3753377308335</v>
+        <v>28.3753377169939</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>1.508916181163134</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.3644876923956364</v>
+        <v>-0.3644876926552238</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>282.3692694331411</v>
+        <v>282.369269433141</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>115.5</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>41.87148631369771</v>
+        <v>41.87148632771403</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>15.60581280158887</v>
+        <v>15.605812903569</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.739033482556843</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-0.9425371319508149</v>
+        <v>-0.9425371323921022</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>41.23425893848425</v>
+        <v>41.23425901363784</v>
       </c>
       <c r="I169" s="2" t="n">
         <v>12.85097660102422</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.0001017772680114437</v>
+        <v>-0.0001017772809913664</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>36.62370328167702</v>
+        <v>36.6237033639153</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>14.69580576821218</v>
+        <v>14.69580599852946</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>1.313538947240605</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.06470771853149021</v>
+        <v>-0.06470771870021558</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>40.599869821764</v>
+        <v>40.59987017755093</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>7.3632155778318</v>
+        <v>7.363215682478851</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.7648272032576218</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.01039803052542188</v>
+        <v>0.01039803044754528</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>277.5342508157365</v>
+        <v>277.5342508157362</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>10.3</v>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>43.52311520113698</v>
+        <v>43.52311509848821</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>26.19186748120674</v>
+        <v>26.19186751352709</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0.9381677593544193</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-0.003443716828752476</v>
+        <v>-0.003443716802794823</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>46.46059921108706</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>14.23547907472326</v>
+        <v>14.23547904760391</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.9560723796159954</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.02694780106901103</v>
+        <v>0.02694780103007277</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>274.106731070282</v>
+        <v>274.106731070284</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>24.4</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>40.52509380958734</v>
+        <v>40.52509370207142</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>17.78936873041507</v>
+        <v>17.78936901168586</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.6188596104281092</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.1617227198771373</v>
+        <v>-0.1617227199160713</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>270.1688436402092</v>
+        <v>270.1688436402097</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>22.45</v>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>36.38947097728289</v>
+        <v>36.38947075145889</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>5.829119515172959</v>
+        <v>5.829119573848169</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.9684550499020043</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-0.05952664855252265</v>
+        <v>-0.05952664840975247</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>268.0428209179114</v>
+        <v>268.0428209179116</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>13.2</v>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>18.97506851453272</v>
+        <v>18.97506882546149</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>56.66765272728573</v>
+        <v>56.66765274163009</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>1.35546585135968</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.09159257789993758</v>
+        <v>0.09159257795185105</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>43.90896119054649</v>
+        <v>43.90896110953394</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>17.63641625446402</v>
+        <v>17.6364165177533</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.5853622963120755</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.02437902718653664</v>
+        <v>-0.02437902719951314</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>262.2039988709605</v>
+        <v>262.2039988709604</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>101</v>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>34.10734969250572</v>
+        <v>34.10734982940762</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>16.56070436180419</v>
+        <v>16.5607044598454</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>1.151863892207114</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-0.3346586046430134</v>
+        <v>-0.3346586052919511</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>43.41313882534249</v>
+        <v>43.41313886371696</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>23.78486383362941</v>
+        <v>23.7848638959556</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>0.6460648573660819</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.295729767805041</v>
+        <v>-0.2957297679478078</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>258.9993416577866</v>
+        <v>258.9993416577855</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>7.86</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>39.74429845376403</v>
+        <v>39.74429879875058</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>16.5142070886295</v>
+        <v>16.51420693515011</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.6674641017909009</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.0006634086983105421</v>
+        <v>-0.0006634087450337611</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>255.075090001261</v>
+        <v>255.0750900012608</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>7.01</v>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>28.25412984104592</v>
+        <v>28.25413010875415</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>21.3117768089671</v>
+        <v>21.31177682662397</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.8383153161487277</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-0.004296269707871558</v>
+        <v>-0.004296269733828656</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>251.8513143456872</v>
+        <v>251.8513143456873</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>172.5</v>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>39.28922258343015</v>
+        <v>39.28922288352346</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>14.42104240352959</v>
+        <v>14.42104236910533</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>1.046525550807784</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.3295352789203672</v>
+        <v>-0.3295352803480049</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>27.21808905626382</v>
+        <v>27.21808911140265</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>15.37296144139088</v>
+        <v>15.37296160035227</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.8918768122737085</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.5434714091838959</v>
+        <v>-0.5434714111307044</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>248.4907275665888</v>
+        <v>248.4907275665884</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>91.2</v>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>36.30664334140145</v>
+        <v>36.30664328990948</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>19.54761833086203</v>
+        <v>19.54761835570364</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>0.8765172249593188</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.9495677162804965</v>
+        <v>-0.9495677161766582</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>245.7477642016691</v>
+        <v>245.747764201669</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>68.5</v>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>37.57156957020904</v>
+        <v>37.57156942718464</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>11.59755052427767</v>
+        <v>11.59755053180661</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>1.201997619142229</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.5423291732432707</v>
+        <v>-0.542329172672203</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>244.5096891249522</v>
+        <v>244.5096891249523</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>299</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>35.40886922030391</v>
+        <v>35.40886924565059</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>14.76245345861662</v>
+        <v>14.76245366744627</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.565533128274054</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-3.033418983789312</v>
+        <v>-3.033418985476501</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>243.9970215776542</v>
+        <v>243.9970215776541</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>0</v>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>45.67822097033981</v>
+        <v>45.67822095853519</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>11.64040729312245</v>
+        <v>11.64040724169471</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.05593945376768674</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>-0.9114449979955017</v>
+        <v>-0.9114449975951238</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>37.39972615674009</v>
+        <v>37.39972624303213</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>16.1555226291458</v>
+        <v>16.15552288408152</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>0.7317270415769943</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-16.09040185136647</v>
+        <v>-16.09040186979605</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>232.9939597222633</v>
+        <v>232.9939597222632</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>43.5</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>36.65526448545924</v>
+        <v>36.65526450368116</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>19.33693751799268</v>
+        <v>19.33693775138033</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.381099686123507</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.6909560372804477</v>
+        <v>-0.690956037423214</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>229.452042134059</v>
+        <v>229.4520421340589</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>33.6</v>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>39.64513711821316</v>
+        <v>39.64513724413143</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>19.03153227429454</v>
+        <v>19.03153236262315</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>1.499289606833824</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.01385940465357411</v>
+        <v>-0.01385940475740292</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>229.0599531549378</v>
+        <v>229.0599531549381</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>9.9</v>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>40.71721907204868</v>
+        <v>40.71721917258004</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>14.35261573862494</v>
+        <v>14.35261565097605</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>1.016587914454049</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.006259320855820746</v>
+        <v>-0.006259320907736787</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>212.9700048639228</v>
+        <v>212.9700048639229</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>23.25</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>41.09699065912254</v>
+        <v>41.09699077550765</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>12.57073019139868</v>
+        <v>12.57073027523811</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.4887745902245083</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.02664916690540154</v>
+        <v>-0.02664916695731736</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>212.0640546739266</v>
+        <v>212.0640546739271</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>29.6</v>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>39.86974533776748</v>
+        <v>39.869745348287</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>19.50407660397317</v>
+        <v>19.5040767090455</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.7544024772416765</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>0.006052818048022157</v>
+        <v>0.006052817970153446</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>205.1325844916774</v>
+        <v>205.1325844916776</v>
       </c>
       <c r="E194" s="2" t="n">
         <v>51</v>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>42.97601317368441</v>
+        <v>42.97601341425057</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>13.0269213989746</v>
+        <v>13.0269215050844</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.3223056363917596</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.009607859526732404</v>
+        <v>-0.009607859578649791</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>194.4986352386992</v>
+        <v>194.4986352386993</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>135</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>43.41537209026253</v>
+        <v>43.41537211419352</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>9.753784558448826</v>
+        <v>9.753784703875709</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>0.4874181713877122</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-1.209921009264495</v>
+        <v>-1.209921010095127</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>194.2749943462482</v>
+        <v>194.2749943462481</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>33.2</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>51.36853792567936</v>
+        <v>51.36853749311306</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>21.87750409716538</v>
+        <v>21.87750444569127</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.5368828427149932</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.29028788652348</v>
+        <v>0.2902878879251772</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>193.9941993623659</v>
+        <v>193.994199362366</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>30.7</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>31.48885487669135</v>
+        <v>31.48885451695187</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>27.1436481190672</v>
+        <v>27.14364817133003</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.9041653475075144</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.1640063169883172</v>
+        <v>-0.1640063169623575</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>187.9115160297327</v>
+        <v>187.9115160297343</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>52</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>41.01119398618346</v>
+        <v>41.01119387885961</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>10.55816252831529</v>
+        <v>10.55816257709748</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>1.332110441083322</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.04266763594119646</v>
+        <v>-0.04266763591524048</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>26.30748203829292</v>
+        <v>26.3074820012407</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>27.4911317057994</v>
+        <v>27.49113181474739</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.7930557691313778</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-1.680101649641806</v>
+        <v>-1.680101649382209</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>186.5716621633109</v>
+        <v>186.571662163311</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>13.95</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>40.77252239887414</v>
+        <v>40.77252248459436</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>18.80420363342829</v>
+        <v>18.804203968253</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>0.8843532663885136</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>0.01280500508741642</v>
+        <v>0.0128050050355016</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>30.5449376778006</v>
+        <v>30.54493776639957</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>18.95124649019461</v>
+        <v>18.95124675026766</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>1.712478540637976</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.1984507114622678</v>
+        <v>-0.1984507122929149</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>179.4876436789488</v>
+        <v>179.4876436789487</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>33</v>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>30.77365849296703</v>
+        <v>30.77365860650808</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>25.30076618431029</v>
+        <v>25.30076628680303</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.9339999489279995</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.2183579293259643</v>
+        <v>-0.2183579296374586</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>29.786947546288</v>
+        <v>29.78694796455264</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>17.82850384236408</v>
+        <v>17.82850385424307</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.9319776067514962</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.1255569515887776</v>
+        <v>-0.1255569519002644</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>38.87811475327899</v>
+        <v>38.87811477252178</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>17.89207039639476</v>
+        <v>17.89207069593362</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.5571983006608549</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.2573976841466526</v>
+        <v>-0.2573976843153787</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>170.1976275970755</v>
+        <v>170.1976275970748</v>
       </c>
       <c r="E205" s="2" t="n">
         <v>67.2</v>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>32.14288453383189</v>
+        <v>32.14288466492475</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>10.0015710637014</v>
+        <v>10.001571050135</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>1.251336455081089</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.3372607411543987</v>
+        <v>-0.337260741543761</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>19.6496016459856</v>
+        <v>19.64960172300412</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>30.9025538712139</v>
+        <v>30.9025539486299</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.6999358688378318</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.07729563649727811</v>
+        <v>-0.07729563662706584</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>165.7176506393199</v>
+        <v>165.7176506393257</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>69</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>24.07398610596192</v>
+        <v>24.07398587255778</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>19.23164307381449</v>
+        <v>19.23164336033934</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>2.700254546406103</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.4478388242127499</v>
+        <v>-0.4478388252510359</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>29.14329705811383</v>
+        <v>29.14329718808997</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>35.36238017100587</v>
+        <v>35.36238016032564</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>1.115437685741795</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.02601769957861433</v>
+        <v>-0.02601769970840295</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>46.99000559248668</v>
+        <v>46.99000563186947</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>18.86295652554444</v>
+        <v>18.86295652290642</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.6275356325917927</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.0401453438770948</v>
+        <v>0.04014534382517877</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>159.5698175173489</v>
+        <v>159.5698175173439</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>17.9</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>36.70291073747858</v>
+        <v>36.70291098720343</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>14.1027102912369</v>
+        <v>14.10271013887794</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>1.50283109067795</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>-0.02652075619680652</v>
+        <v>-0.02652075641743989</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>23.36629808652994</v>
+        <v>23.36629830769334</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>16.63887749437874</v>
+        <v>16.63887793788815</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.5973835181697705</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-1.207216737171386</v>
+        <v>-1.207216740545845</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>44.29174373809646</v>
+        <v>44.29174347944276</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>16.57498850555966</v>
+        <v>16.57498851618674</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>1.114313073778932</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.03098193803533095</v>
+        <v>-0.03098193790554116</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>34.12301280036193</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>19.29769820969803</v>
+        <v>19.29769840997176</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.1656159786474881</v>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>39.57811607033721</v>
+        <v>39.57811602276033</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>18.00270558970625</v>
+        <v>18.00270581448142</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.8469336381748296</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>0.1350142118296703</v>
+        <v>0.1350142116998726</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>40.77406524079424</v>
+        <v>40.77406531491427</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>16.62272530786504</v>
+        <v>16.62272532721743</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.9888867931416332</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.1271844379581744</v>
+        <v>-0.1271844380879619</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>33.78258891475487</v>
+        <v>33.782589171019</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>18.07401040655304</v>
+        <v>18.0740103685713</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>1.603963970321794</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.06537947559461155</v>
+        <v>-0.06537947585419437</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>108.5243440680159</v>
+        <v>108.5243440680161</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>19.05</v>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>30.70588286631097</v>
+        <v>30.70588295645706</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>14.32493790721668</v>
+        <v>14.32493808450611</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.8274137709532717</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.1208589796643873</v>
+        <v>-0.1208589797682191</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>96.37311404964997</v>
+        <v>96.3731140496498</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>16.05</v>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>43.39718463503124</v>
+        <v>43.39718468753433</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>14.03923114810032</v>
+        <v>14.03923112290522</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.9521462223742636</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.07488387531922847</v>
+        <v>0.07488387522135936</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>93.74941726617955</v>
+        <v>93.74941726616755</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>22.95</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>35.67537605613603</v>
+        <v>35.67537594410362</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>13.94353791943927</v>
+        <v>13.94353834454118</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.7697212295967318</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.06769194200786866</v>
+        <v>-0.06769194177425436</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>39.55226318510067</v>
+        <v>39.5522632708687</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>18.04406400032497</v>
+        <v>18.04406406015421</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.431320706959155</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.2833578442910257</v>
+        <v>-0.2833578446025152</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>84.12079975036005</v>
+        <v>84.12079975035948</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>25.55</v>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>34.32202134977477</v>
+        <v>34.32202142166081</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>16.98733234872322</v>
+        <v>16.98733231958501</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>0.6726405655023939</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.1751766395892441</v>
+        <v>-0.175176639757968</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>83.59668369235011</v>
+        <v>83.59668369235024</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>36.4</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>36.8891802239636</v>
+        <v>36.8891802079315</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>18.8866908020741</v>
+        <v>18.88669088840311</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>1.212801155523601</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>-0.07602743236671816</v>
+        <v>-0.07602743244459498</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v/>
       </c>
       <c r="D223" s="2" t="n">
-        <v>81.47835301545135</v>
+        <v>81.47835301545119</v>
       </c>
       <c r="E223" s="2" t="n">
         <v>30.1</v>
@@ -12265,10 +12265,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>43.54767234681381</v>
+        <v>43.54767245063795</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>9.930554766747209</v>
+        <v>9.93055481450132</v>
       </c>
       <c r="J223" s="2" t="n">
         <v>0.5676490569924377</v>
@@ -12283,7 +12283,7 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>-0.05807857822883292</v>
+        <v>-0.05807857833266733</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>42.94993819140942</v>
+        <v>42.94993808031622</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>14.50363409718982</v>
+        <v>14.50363410182314</v>
       </c>
       <c r="J224" s="2" t="n">
         <v>0.6724353993634521</v>
@@ -12357,7 +12357,7 @@
         <v/>
       </c>
       <c r="D225" s="2" t="n">
-        <v>66.1410378010939</v>
+        <v>66.14103780109539</v>
       </c>
       <c r="E225" s="2" t="n">
         <v>50.6</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>28.29126101359918</v>
+        <v>28.29126103033154</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>15.67624574238054</v>
+        <v>15.67624578618235</v>
       </c>
       <c r="J225" s="2" t="n">
         <v>0.6132828671121887</v>
@@ -12389,7 +12389,7 @@
         <v>-1</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>-0.2638414038525447</v>
+        <v>-0.263841404631266</v>
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v/>
       </c>
       <c r="D226" s="2" t="n">
-        <v>50.87955968601678</v>
+        <v>50.87955968601688</v>
       </c>
       <c r="E226" s="2" t="n">
         <v>9.380000000000001</v>
@@ -12424,10 +12424,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>29.50217479334469</v>
+        <v>29.50217403218842</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>18.99355970788609</v>
+        <v>18.99355976742135</v>
       </c>
       <c r="J226" s="2" t="n">
         <v>0.6960673559347924</v>
@@ -12442,7 +12442,7 @@
         <v>-1</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>-0.1524393982787821</v>
+        <v>-0.1524393978517128</v>
       </c>
       <c r="O226" s="2" t="inlineStr">
         <is>
@@ -12477,10 +12477,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>40.1268794253444</v>
+        <v>40.1268795356326</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>7.975730033696197</v>
+        <v>7.97573017906528</v>
       </c>
       <c r="J227" s="2" t="n">
         <v>1.231777474530908</v>
@@ -12495,7 +12495,7 @@
         <v>-1</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>-0.08036340324940527</v>
+        <v>-0.08036340362579439</v>
       </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v/>
       </c>
       <c r="D228" s="2" t="n">
-        <v>42.09182382773901</v>
+        <v>42.09182382772433</v>
       </c>
       <c r="E228" s="2" t="n">
         <v>87</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>33.87776207536538</v>
+        <v>33.87776184894709</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>18.47498690973342</v>
+        <v>18.47498685443718</v>
       </c>
       <c r="J228" s="2" t="n">
         <v>1.249969307849761</v>
@@ -12548,7 +12548,7 @@
         <v>-1</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>-0.3472455167579187</v>
+        <v>-0.347245516498341</v>
       </c>
       <c r="O228" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq2_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq2_2026-10-22.xlsx
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.01152128381725</v>
+        <v>72.01152127699748</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>36.97312965608842</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>87.24456239433516</v>
+        <v>87.24456226091704</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>53.62495541844681</v>
+        <v>53.62495541370284</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.482726485597089</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.8166764682052889</v>
+        <v>0.8166764684856327</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.37825775986849</v>
+        <v>66.37825765685047</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.37331902938807</v>
+        <v>33.3733191185739</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.121547089493213</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.05824093139206743</v>
+        <v>-0.05824093142010334</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.88648203316824</v>
+        <v>68.88648209428746</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>42.44150054449345</v>
+        <v>42.4415006411718</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.291744269371122</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4728042981922354</v>
+        <v>0.4728042980240335</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.18160926675926</v>
+        <v>61.18160930090496</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>22.06221627988486</v>
+        <v>22.06221634070737</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>5.49373864515799</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.01444191125032018</v>
+        <v>0.01444191122228711</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.98619290243865</v>
+        <v>61.98619288942696</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>27.15708878009825</v>
+        <v>27.15708872119094</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.8469311963211047</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.8258859022746101</v>
+        <v>0.8258859024147838</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>968.6825189208938</v>
+        <v>968.6825189208937</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>19.55</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>61.76330080081663</v>
+        <v>61.76330090926378</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33.4178208210438</v>
+        <v>33.41782089585882</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1.160238568251936</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.06356760766274779</v>
+        <v>0.06356760760668062</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>58.76239797321045</v>
+        <v>58.76239837258105</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.59333450303726</v>
+        <v>14.59333454080632</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>2.14542212383939</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.008803846056288318</v>
+        <v>0.008803846042268328</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>939.2120612408211</v>
+        <v>939.212061240821</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>50.6</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>62.21882386180707</v>
+        <v>62.21882376076758</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>31.49038758542867</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2284785763627134</v>
+        <v>0.2284785764187832</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.81324855473989</v>
+        <v>64.81324850424966</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>37.72202506519466</v>
+        <v>37.7220251529494</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.219956408623487</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1265130133282014</v>
+        <v>0.1265130134683747</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>862.6390992617413</v>
+        <v>862.6390992617411</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>53.6</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>72.48000145355144</v>
+        <v>72.48000183972783</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33.75083676230297</v>
+        <v>33.7508369685262</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>5.905504304893155</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.5441570613295028</v>
+        <v>0.5441570605165202</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>836.8504547414778</v>
+        <v>836.850454741478</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>67.8</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>59.50442554972993</v>
+        <v>59.50442562491872</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14.7822569724705</v>
+        <v>14.78225699910449</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.7260814030032949</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.03318708806438575</v>
+        <v>0.03318708786813429</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.98125435147196</v>
+        <v>57.98125457723255</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15.56253826387973</v>
+        <v>15.56253836746445</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.441759146664404</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.09533824181396777</v>
+        <v>0.09533824171584657</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>81.06958699301771</v>
+        <v>81.06958699905972</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>60.39163056405715</v>
+        <v>60.39163058344258</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1.054767956119938</v>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>820.2838287964305</v>
+        <v>820.2838287964307</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>47</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.84545847157158</v>
+        <v>59.84545852790522</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.29984277700484</v>
+        <v>22.29984304845056</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>2.168957906239822</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1172801233317518</v>
+        <v>0.1172801231915801</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.66308975437022</v>
+        <v>56.6630898015022</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.6996137967266</v>
+        <v>31.69961412274235</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.750187145687303</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.25322086231892</v>
+        <v>1.253220861057378</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>809.9146853372497</v>
+        <v>809.9146853372496</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>11.65</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.8702864890967</v>
+        <v>60.87028644551353</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31.0670070564492</v>
+        <v>31.06700708269425</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.9634403283350106</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.06504436918031667</v>
+        <v>0.06504436919366119</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.32165219627097</v>
+        <v>51.32165221084539</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.25612691051505</v>
+        <v>28.25612697673122</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.760879485801488</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.03523733238986909</v>
+        <v>0.03523733241790117</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>790.9790975145099</v>
+        <v>790.97909751451</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>772</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.69674014301808</v>
+        <v>55.69674007886982</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28.30654556309412</v>
+        <v>28.30654556456378</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.9568104824451327</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.700372717885653</v>
+        <v>1.700372719287367</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>54.8546372662521</v>
+        <v>54.8546372607634</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.4721385808865</v>
+        <v>31.47213860198791</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.4455587567304397</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.274113475215666</v>
+        <v>-0.2741134752016507</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>786.2147688757001</v>
+        <v>786.2147688757</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>124</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.2107102198561</v>
+        <v>50.21071005168087</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16.13755016667206</v>
+        <v>16.13755019761249</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.962348391481295</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1758350864791316</v>
+        <v>0.1758350868996357</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>60.55226802869725</v>
+        <v>60.55226820110455</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>30.46580656351762</v>
+        <v>30.46580679840203</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>2.943431122394263</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.4880348799887002</v>
+        <v>0.4880348791056253</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>767.4879204168826</v>
+        <v>767.4879204168822</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>29.4</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>53.88409830639194</v>
+        <v>53.88409855610844</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20.3465895115729</v>
+        <v>20.34658968216477</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>1.182865639882094</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.03181298678003004</v>
+        <v>0.03181298689124372</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>54.70273956364665</v>
+        <v>54.70273962393999</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>33.87696016817376</v>
+        <v>33.87696027489386</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>2.200009827261391</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.1859337245966008</v>
+        <v>-0.185933724694721</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>44.16082212943967</v>
+        <v>44.1608221392675</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15.87637359377039</v>
+        <v>15.8763736023526</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.732198741499918</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-63.25340764388201</v>
+        <v>-63.25340764528396</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.57794359717469</v>
+        <v>49.57794359017048</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>30.36006910038712</v>
+        <v>30.36006911172971</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.7828541872483388</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.9164691083867624</v>
+        <v>-0.9164691083727461</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>740.5916139940608</v>
+        <v>740.5916139940607</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>28.3</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.87779665890348</v>
+        <v>55.87779673229952</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.90227291402267</v>
+        <v>26.90227293898436</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.38751345532831</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.01162391852694564</v>
+        <v>-0.01162391856899644</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>737.0709026497364</v>
+        <v>737.0709026497341</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>44.95</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.28752470552211</v>
+        <v>54.28752471920394</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>31.98403810325876</v>
+        <v>31.98403827405648</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.9871419424109069</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.06599900977178796</v>
+        <v>0.06599900968768591</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>64.6486820334523</v>
+        <v>64.64868205254335</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.87613744975975</v>
+        <v>27.87613752800144</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.8637118404807616</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1833789077278383</v>
+        <v>0.1833789076857877</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.75091488385754</v>
+        <v>51.75091489432114</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.4481097510965</v>
+        <v>16.44810975109651</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.9106424168101875</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2210650448361944</v>
+        <v>0.2210650448782433</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.41761546427496</v>
+        <v>51.41761549599492</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>27.80263524025635</v>
+        <v>27.80263530103207</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.8988394129954463</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4915053934674587</v>
+        <v>0.4915053933693407</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.11558967366371</v>
+        <v>51.11558967911126</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24.14116027052971</v>
+        <v>24.14116028654338</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>1.367489313772294</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>70.58901047887511</v>
+        <v>70.58901043121803</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>53.61155817241053</v>
+        <v>53.61155812093289</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1.130774262600237</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1082664549290412</v>
+        <v>0.1082664549430603</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>65.37325280218914</v>
+        <v>65.37325282368339</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>29.72074055577313</v>
+        <v>29.72074057329105</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.025606667386425</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.9048303255908152</v>
+        <v>-0.9048303257309858</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>695.2851948727274</v>
+        <v>695.2851948727272</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>99.3</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>60.33236227271571</v>
+        <v>60.33236233730712</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46.24346692963582</v>
+        <v>46.24346724950416</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.83997571841871</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.1127385583271772</v>
+        <v>-0.1127385587476883</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>68.42758922581473</v>
+        <v>68.42758924448115</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>35.65782097509138</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.07237469660335999</v>
+        <v>0.07237469661737822</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>47.8311240397087</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.34318189921417</v>
+        <v>37.34318198564861</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.508621970714119</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.1507637795698498</v>
+        <v>-0.1507637795978878</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.49290210859566</v>
+        <v>52.49290212009328</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>34.99943255978155</v>
+        <v>34.99943267065026</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.5659887137495955</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.4265559720940755</v>
+        <v>-0.4265559721641579</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>667.2038570154873</v>
+        <v>667.2038570154872</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>23.1</v>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.56022367043749</v>
+        <v>58.56022358959406</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.96076794198</v>
+        <v>20.96076796902731</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.8160339894195259</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.05540469857680347</v>
+        <v>0.05540469859082442</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.05761320208011</v>
+        <v>48.05761327731572</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>34.89878876278864</v>
+        <v>34.89878880843136</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.6957602134886265</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.4157986626601468</v>
+        <v>-0.415798662786296</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.84656204876762</v>
+        <v>51.84656202554634</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.1328288059734</v>
+        <v>18.13282869590487</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.7303460114355046</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.4228739145766496</v>
+        <v>0.4228739148570382</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46.63085865399727</v>
+        <v>46.63085869639711</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29.19474597372984</v>
+        <v>29.19474608438816</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.7748970947860256</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-10.55767331994282</v>
+        <v>-10.55767332597024</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>646.5069385341952</v>
+        <v>646.5069385341949</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>31.45</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.38621300565264</v>
+        <v>56.386213217018</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.98378591479959</v>
+        <v>21.98378603479505</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.7383573143368219</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.02142753769861631</v>
+        <v>0.02142753761451539</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>626.5073836921174</v>
+        <v>626.5073836921172</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>79.40000000000001</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.30985543113707</v>
+        <v>50.30985549932716</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.25622077568508</v>
+        <v>22.25622071419011</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.7729220504468551</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2000685318890202</v>
+        <v>0.2000685314685057</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.73086208455761</v>
+        <v>56.73086218803603</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.26293565680193</v>
+        <v>16.26293572869251</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.5811173776953098</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.08212362698370712</v>
+        <v>0.08212362681550617</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>44.70157145801519</v>
+        <v>44.70157149281252</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.63569453295286</v>
+        <v>16.63569463644767</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.7727158534581907</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.6039119327204077</v>
+        <v>-0.6039119334212284</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>613.5127475320402</v>
+        <v>613.5127475320398</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>74</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.12952026089461</v>
+        <v>51.12952034057174</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>29.36745150378813</v>
+        <v>29.36745177564034</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>0.5735088920435083</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.06711901989621083</v>
+        <v>-0.06711902084936128</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.91218033326587</v>
+        <v>44.91218056651314</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>26.62838227876462</v>
+        <v>26.6283823351682</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.3977578603644275</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.2171792802011199</v>
+        <v>-0.2171792806216303</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>608.9250430918787</v>
+        <v>608.9250430918786</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>245</v>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.32303863429754</v>
+        <v>47.32303867521861</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>9.161953961365315</v>
+        <v>9.161953978398731</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.6450825324256385</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.62229152080832</v>
+        <v>46.62229179880189</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20.46222010625021</v>
+        <v>20.46222010747433</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.4418527200123052</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.6301830416454673</v>
+        <v>-0.6301830417716157</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>602.1504702209094</v>
+        <v>602.1504702209093</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>224.5</v>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.07575777308143</v>
+        <v>44.07575779883206</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.64129135645552</v>
+        <v>20.64129131472876</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.264012772908557</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.50975784212942</v>
+        <v>-1.509757842493849</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>51.73033791792935</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.68397939377476</v>
+        <v>24.68397947752718</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.3423168728970312</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.05828282063313872</v>
+        <v>-0.05828282066117416</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.80039762489012</v>
+        <v>49.80039758995949</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>42.40923417830059</v>
+        <v>42.40923422401502</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.5576037116275411</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.12440072629404</v>
+        <v>-0.1244007262660073</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>59.95827446712548</v>
+        <v>59.95827436633217</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>37.00015005278764</v>
+        <v>37.00015008212244</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>1.084337245314478</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.04281863214243553</v>
+        <v>-0.04281863212841813</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>591.4928400487122</v>
+        <v>591.4928400487121</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>63.4</v>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.17672299567712</v>
+        <v>50.17672263292757</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.39938157328661</v>
+        <v>22.39938193306972</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.4497034798590612</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1455220975801833</v>
+        <v>-0.1455220973278799</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.15400753601283</v>
+        <v>54.15400765138163</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.53230278411035</v>
+        <v>26.53230279472488</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>1.920458338773163</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.05792086660891496</v>
+        <v>-0.05792086669301427</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>56.11535908013342</v>
+        <v>56.11535904342076</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>38.44035978620812</v>
+        <v>38.44035973638432</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.5444527600209411</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.03189287768382981</v>
+        <v>-0.03189287766981397</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45.42817077191017</v>
+        <v>45.42817077590092</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.32023233048425</v>
+        <v>22.3202324062697</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.4470308669276036</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.2603695860961381</v>
+        <v>-0.2603695862082814</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>54.47082252276194</v>
+        <v>54.47082252891435</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>31.34601849591558</v>
+        <v>31.3460184846645</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.5038978563807209</v>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>567.2261334110013</v>
+        <v>567.2261334110034</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>30.55</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46.99577681056817</v>
+        <v>46.99577667277212</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>60.96233897916145</v>
+        <v>60.96233883845039</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.7322735536804811</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.03205231395488914</v>
+        <v>-0.03205231384275355</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>564.5326063490808</v>
+        <v>564.5326063490809</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>50.7</v>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>63.94336931783591</v>
+        <v>63.94336952852625</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>38.15514316363071</v>
+        <v>38.15514328633504</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.536237710032485</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.4917566868717267</v>
+        <v>0.4917566867035195</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>558.3921197980411</v>
+        <v>558.392119798041</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>33.15</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.5450933118106</v>
+        <v>49.54509350034465</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>26.48341674678545</v>
+        <v>26.48341691854824</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.855381171753604</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.02456174722636692</v>
+        <v>-0.02456174728243032</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.85041667766748</v>
+        <v>52.85041680260727</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>23.68558809985667</v>
+        <v>23.68558816305119</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.5629531268076031</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.04430804756092332</v>
+        <v>0.04430804758895798</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.5833650362486</v>
+        <v>54.58336516168282</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.43520698023605</v>
+        <v>12.4352070199722</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.5212972976237145</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.56092933366212</v>
+        <v>46.56092936523395</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>41.15910308025366</v>
+        <v>41.15910317001352</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.3098762123545035</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.06047829435953039</v>
+        <v>0.06047829434551241</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>549.3090398973355</v>
+        <v>549.3090398973357</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>56.5</v>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>57.56116279392726</v>
+        <v>57.56116261867034</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>53.53133447365472</v>
+        <v>53.53133450772916</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.6880925206509628</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.383880738564351</v>
+        <v>-0.3838807381718752</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>33.26367547200719</v>
+        <v>33.26367553461272</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.48884234029382</v>
+        <v>22.48884230381181</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.7055749475968663</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-148.6354741993787</v>
+        <v>-148.6354742091905</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>56.30046725608516</v>
+        <v>56.30046727530057</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.65216924506242</v>
+        <v>13.65216943116155</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1.154782751603843</v>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>54.43068039805571</v>
+        <v>54.43068043001357</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.47696056735744</v>
+        <v>16.47696062318133</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.7000791229251062</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.09630391929850438</v>
+        <v>0.09630391922841949</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.29664978617273</v>
+        <v>44.29664982377437</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14.25953497275385</v>
+        <v>14.25953511740339</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.672378374143566</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.83153001282972</v>
+        <v>-1.831530013670757</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.78337696804693</v>
+        <v>50.78337700239359</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.62417413962514</v>
+        <v>20.62417401679663</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.5834968729702051</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1494235411807477</v>
+        <v>0.1494235411327065</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>40.83385381717951</v>
+        <v>40.83385398975353</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23.55428445845613</v>
+        <v>23.55428452018483</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.3036153438054449</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-22.92220494782335</v>
+        <v>-22.9222049814642</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>53.21163987147064</v>
+        <v>53.21163992540611</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.16876092499805</v>
+        <v>16.16876106143669</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.7506520411068461</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.01735493933330993</v>
+        <v>-0.01735493936134376</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>55.44384195100353</v>
+        <v>55.44384194811413</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>39.54960903625241</v>
+        <v>39.54960914516845</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.6098231876927032</v>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.13948377023222</v>
+        <v>47.13948377880866</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>44.55110336452399</v>
+        <v>44.55110338608597</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.486064468593901</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.166031766475342</v>
+        <v>-2.166031766461328</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.47233613455456</v>
+        <v>50.47233600763101</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>56.91558600459078</v>
+        <v>56.91558611356479</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.575801946174918</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.04835275843966591</v>
+        <v>-0.04835275836957992</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>505.9373801742294</v>
+        <v>505.9373801742298</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>30.5</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>56.20738100147804</v>
+        <v>56.20738113799875</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.98203736871284</v>
+        <v>18.98203749284821</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>2.741423071238442</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.07417081462750377</v>
+        <v>-0.07417081482374144</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.9691660597827</v>
+        <v>51.96916612728339</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.17647729732905</v>
+        <v>17.17647727912551</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.6757950658167228</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.01467256992465439</v>
+        <v>0.01467256991063676</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>54.20941003294092</v>
+        <v>54.20940990342764</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>38.03621085728004</v>
+        <v>38.03621089198037</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.4699885038300045</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.08679133084748014</v>
+        <v>0.08679133079140855</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.85022684211369</v>
+        <v>48.85022713352625</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>22.87358162888154</v>
+        <v>22.87358169973054</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.5743380799575032</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1193404712299771</v>
+        <v>-0.1193404711458731</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.84674749294749</v>
+        <v>48.84674751971159</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.14637911283667</v>
+        <v>16.14637904511835</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.4886890856759769</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.4258643230357048</v>
+        <v>-0.4258643230216851</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>38.32230278431655</v>
+        <v>38.32230280209814</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.92527774712975</v>
+        <v>22.92527782197724</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.4464089368305957</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.6858066148235286</v>
+        <v>-0.6858066148795965</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>52.99037879680964</v>
+        <v>52.9903788336013</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>37.72164858334081</v>
+        <v>37.72164862804115</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.5136415914373952</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.616744595501721</v>
+        <v>-0.6167445955437771</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>47.68236875012133</v>
+        <v>47.68236871497837</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.81555682872665</v>
+        <v>18.81555685263211</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.3874886152781585</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0760058311801082</v>
+        <v>-0.0760058311520746</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.72909610946633</v>
+        <v>45.72909617118123</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.4197599767136</v>
+        <v>15.41976013834168</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.5881016056062572</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1257958080132409</v>
+        <v>-0.1257958080973406</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.0570987734384</v>
+        <v>51.05709888483246</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>37.30629773350044</v>
+        <v>37.30629792541563</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.4386498455795602</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.02430973640500289</v>
+        <v>-0.02430973646107121</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>51.87719466575076</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>29.72677848806405</v>
+        <v>29.726778623882</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.5011552354874401</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.08123785939651185</v>
+        <v>-0.08123785939931161</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.33793599299686</v>
+        <v>48.33793596637926</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>34.6118466920385</v>
+        <v>34.61184680455895</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.7090793648329287</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.05159290605896566</v>
+        <v>-0.05159290604775196</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.80163518359259</v>
+        <v>43.80163512954302</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>30.21849597717921</v>
+        <v>30.21849585784574</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>1.167602265069588</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2203852930331489</v>
+        <v>0.2203852931452773</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>54.177303046787</v>
+        <v>54.17730305991438</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>26.20762963501019</v>
+        <v>26.20762951886691</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0.8698553255406335</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.04242767088141122</v>
+        <v>0.04242767092346361</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.17568105404067</v>
+        <v>42.17568107488231</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21.62963167158804</v>
+        <v>21.62963181519368</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.3074233721273395</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-2.153473673362985</v>
+        <v>-2.153473673839564</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.0799419243948</v>
+        <v>49.07994195187358</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>44.38769004569455</v>
+        <v>44.38769016261842</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.715034821669062</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.6284025622311211</v>
+        <v>-0.6284025621750535</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>448.2198754428018</v>
+        <v>448.2198754428017</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>14.7</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>55.1600892133005</v>
+        <v>55.16008928332857</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.24904693598768</v>
+        <v>16.24904697745051</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.7880518068979494</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.06432485326266753</v>
+        <v>0.06432485323463515</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45.06190774836685</v>
+        <v>45.06190781436021</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.22275724870133</v>
+        <v>15.22275725839531</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.1811770112229872</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.02881370800554478</v>
+        <v>0.02881370796349469</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>33.77596683612839</v>
+        <v>33.77596683417133</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.21008121233188</v>
+        <v>20.21008121536802</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.8719064807750735</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-38.98952223798647</v>
+        <v>-38.9895222388275</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>24.03413484838599</v>
+        <v>24.03352361925658</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>38.88078230682346</v>
+        <v>38.87798074375622</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>4.024376545896833</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.09872439778424713</v>
+        <v>0.09872227082049667</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.10454507009941</v>
+        <v>46.10454509995606</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>28.26209764489364</v>
+        <v>28.26209764507099</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.7805558426368758</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.3069868415387287</v>
+        <v>-0.3069868412023249</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.56172967278525</v>
+        <v>51.5617297388356</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>35.02520162455451</v>
+        <v>35.02520158366688</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.3106206944549773</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1764715395696268</v>
+        <v>-0.1764715396116761</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.23118453685744</v>
+        <v>41.23118487416119</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.84855182149285</v>
+        <v>11.84855199163855</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.7776832763664637</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1689579675222656</v>
+        <v>-0.1689579679147541</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>51.88894886834126</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.1042974157168</v>
+        <v>17.10429743560069</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.457145239940278</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1182300723175367</v>
+        <v>-0.1182300723455709</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>422.7527493536178</v>
+        <v>422.7527493536177</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>2385</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>37.80757258327821</v>
+        <v>37.80757259488443</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>20.06587438544054</v>
+        <v>20.06587435900915</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>1.092061727717139</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-18.44774036194905</v>
+        <v>-18.4477403633509</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>38.3698318978108</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>23.54669705799797</v>
+        <v>23.54669719746033</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.4344532034917649</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.3890001846130985</v>
+        <v>-0.3890001846271215</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.42556968204831</v>
+        <v>49.42556952020338</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.34332670588721</v>
+        <v>13.34332673415586</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.8986742550231747</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.02516306229459622</v>
+        <v>0.02516306228057827</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>50.10806586859859</v>
+        <v>50.10806548464328</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.23999617639458</v>
+        <v>14.23999617979069</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.7494444373144629</v>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>412.6468741318903</v>
+        <v>412.6468741318902</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>1980</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.7966724681844</v>
+        <v>39.79667246193654</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.64278077351065</v>
+        <v>15.64278082824849</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>0.835728833314724</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-37.96644099306841</v>
+        <v>-37.96644099390986</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>411.9205697005818</v>
+        <v>411.9205697005801</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>154.5</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.04310383576986</v>
+        <v>40.04310384222723</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.51392691747885</v>
+        <v>14.51392691295591</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.6622104319679991</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-2.015451016623527</v>
+        <v>-2.015451016721636</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.98079928636888</v>
+        <v>43.98079931496847</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>33.92675243413379</v>
+        <v>33.92675253178408</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.4142592357494622</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.5354356149486874</v>
+        <v>-0.5354356150327912</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>407.5655515414895</v>
+        <v>407.5655515414894</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>39.7</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>31.3958348981362</v>
+        <v>31.39583503075534</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>32.37754972434309</v>
+        <v>32.37754971890324</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.5937912816083324</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.01916104943841046</v>
+        <v>0.01916104949448383</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.58645417038232</v>
+        <v>46.5864544299915</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>22.64206677084688</v>
+        <v>22.64206693012814</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.6722876356748286</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1705990414450657</v>
+        <v>0.1705990409124156</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45.05969159488107</v>
+        <v>45.05969162436909</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.18122852191815</v>
+        <v>19.18122849965848</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>1.200305590745833</v>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>397.3458914834493</v>
+        <v>397.3458914834471</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>17.25</v>
@@ -6435,7 +6435,7 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.86068437317296</v>
+        <v>35.86068427783128</v>
       </c>
       <c r="I113" s="2" t="n">
         <v>40.9981915134596</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.05352756634951789</v>
+        <v>-0.05352756640558488</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.02974694136984</v>
+        <v>40.0297469912149</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.15466335449518</v>
+        <v>20.15466349587236</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.8273680744464309</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-2.708792092450175</v>
+        <v>-2.70879209259033</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>41.54640854208773</v>
+        <v>41.54640893848955</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.83487393168418</v>
+        <v>19.83487381314676</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>1.736104627937512</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.06396358944030472</v>
+        <v>-0.06396358935620428</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.80598865555593</v>
+        <v>44.80598841215443</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>5.723190909352819</v>
+        <v>5.723190806650733</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.7346377442266808</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.01015735791485808</v>
+        <v>-0.0101573578447731</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>27.65934311608689</v>
+        <v>27.65934313611892</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>25.58184084445951</v>
+        <v>25.58184098689041</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.9021606381539965</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.2095421679387447</v>
+        <v>-0.2095421680088311</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>388.3665423841375</v>
+        <v>388.3665423841363</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>414</v>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>33.69826424409574</v>
+        <v>33.69826425168297</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>21.60311240505059</v>
+        <v>21.60311243033381</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.7034620968874117</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-10.93307122201802</v>
+        <v>-10.9330712223264</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>388.0599836370025</v>
+        <v>388.0599836370024</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>28.7</v>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>45.68698924161206</v>
+        <v>45.6869892246029</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>23.39729930574676</v>
+        <v>23.39729930823957</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.7144441596936296</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.04309037879605493</v>
+        <v>-0.0430903788521243</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>48.66369955868458</v>
+        <v>48.66369954649535</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>41.23398732997928</v>
+        <v>41.23398737793249</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>1.194863568448148</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>1.436137121430193</v>
+        <v>1.436137121570361</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>47.88810082903944</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.59641015228948</v>
+        <v>18.59641036580292</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>1.28196601692693</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.02860764550428264</v>
+        <v>0.02860764554633504</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>385.376265460336</v>
+        <v>385.3762654603358</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>165</v>
@@ -6912,7 +6912,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.77525276696832</v>
+        <v>45.77525303907629</v>
       </c>
       <c r="I122" s="2" t="n">
         <v>25.44304081025736</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-1.25132874827006</v>
+        <v>-1.2513287499521</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>38.4449070777007</v>
+        <v>38.44490713850084</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>20.03654605196363</v>
+        <v>20.03654625449494</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>1.082218677928881</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-2.127794906542099</v>
+        <v>-2.127794907383103</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>40.57030253338733</v>
+        <v>40.57030265395149</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>25.2211759003664</v>
+        <v>25.22117601373121</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.1830506540752569</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-1.021371258053758</v>
+        <v>-1.021371258165898</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46.45378039543859</v>
+        <v>46.45378029177029</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>20.91367871709222</v>
+        <v>20.91367877173623</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.6455668080909884</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>33.44025785806591</v>
+        <v>33.44025801615494</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>25.32554532996899</v>
+        <v>25.32554535659626</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>1.496141996711587</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0168201348993938</v>
+        <v>0.01682013481529085</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>376.1703350512393</v>
+        <v>376.1703350512394</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>10.1</v>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>48.48806664457013</v>
+        <v>48.48806643962338</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>17.94007986237215</v>
+        <v>17.94007985025354</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>1.00592323465078</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.003141606770301689</v>
+        <v>0.003141606798336158</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>374.3240104449597</v>
+        <v>374.3240104449594</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>9.69</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>48.33578463111722</v>
+        <v>48.33578449807375</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>14.20594720650877</v>
+        <v>14.20594732874613</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>1.48755947772858</v>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>373.0650548314325</v>
+        <v>373.065054831433</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>44.95</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>50.23435030714446</v>
+        <v>50.23435039491712</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>31.26413344224337</v>
+        <v>31.26413340682777</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.9091880319532467</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.1080608890882491</v>
+        <v>-0.1080608893826022</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>371.203776480429</v>
+        <v>371.2037764804289</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>42.4</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>23.1745235605693</v>
+        <v>23.17452380222196</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>37.40535048512301</v>
+        <v>37.40535048531106</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>1.551192223326863</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.08748139945524569</v>
+        <v>-0.08748139948327949</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>48.40562540382759</v>
+        <v>48.40562518544158</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>17.60929475770435</v>
+        <v>17.60929480066947</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>1.37652197500104</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.05235255364003338</v>
+        <v>-0.05235255366806606</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>362.9104249482139</v>
+        <v>362.9104249482235</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>99.5</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>33.29238003694897</v>
+        <v>33.29238003924679</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>20.01417023013257</v>
+        <v>20.01417024945906</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.9772696762944962</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-1.458584842080443</v>
+        <v>-1.458584842136528</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>30.83847979631722</v>
+        <v>30.8384811841415</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>26.36624517289241</v>
+        <v>26.36624546530053</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.6282760169832019</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.07242840597498298</v>
+        <v>-0.07242840619925187</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>353.4146288081522</v>
+        <v>353.4146288081934</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>12.65</v>
@@ -7587,7 +7587,7 @@
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>351.5687460295065</v>
+        <v>351.5687460295063</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>10</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>47.66679111497716</v>
+        <v>47.66679153518064</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>13.63532225352751</v>
+        <v>13.635322227871</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.5514827953515301</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.001610711115834031</v>
+        <v>-0.001610711185919336</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>42.79420096286727</v>
+        <v>42.79420101718529</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>12.07400251860253</v>
+        <v>12.07400254119076</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.4959012731108359</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.1204959363615772</v>
+        <v>-0.1204959363475566</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>348.9422908625989</v>
+        <v>348.9422908625988</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>38.5</v>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>43.21014051536695</v>
+        <v>43.21014057261085</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>25.37721211890972</v>
+        <v>25.37721213896047</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.4887912607820229</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.1394412347067054</v>
+        <v>-0.1394412346786787</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>348.8941405443043</v>
+        <v>348.8941405443042</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>52.6</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>40.75299843695109</v>
+        <v>40.7529985782974</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>21.77948113686539</v>
+        <v>21.77948125595256</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.3518106111886002</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.7875726062993356</v>
+        <v>-0.7875726066637794</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>5.069932061131354</v>
+        <v>5.069932111024926</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>22.14607552692666</v>
+        <v>22.14607552919753</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>7.507704782032561e-05</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-2.944063455186526</v>
+        <v>-2.944063455242591</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>38.90210361039235</v>
+        <v>38.90210368331142</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>19.09666043325018</v>
+        <v>19.09666045987691</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.4674163989451693</v>
@@ -7905,7 +7905,7 @@
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>343.7186144757103</v>
+        <v>343.7186144757105</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>7</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>52.24883304470157</v>
+        <v>52.24883309868935</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>15.46697571560827</v>
+        <v>15.46697572200181</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>0.9150693411207079</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.01192428104652935</v>
+        <v>0.01192428105493857</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>335.5221687409956</v>
+        <v>335.5221687409964</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>26.65</v>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>38.76512523659039</v>
+        <v>38.76512546903991</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>17.78844487042035</v>
+        <v>17.78844483057045</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0.6885351780687545</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.03179534806424422</v>
+        <v>-0.03179534851278842</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>27.25898867953067</v>
+        <v>27.25898872906382</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>39.22977624247041</v>
+        <v>39.22977619433754</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.6339276652623533</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.01629111680942263</v>
+        <v>0.01629111679540124</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>329.8779379006592</v>
+        <v>329.8779379006594</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>37.6</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>45.53122126855208</v>
+        <v>45.53122137890991</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>20.54379987542599</v>
+        <v>20.54380007251087</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.5509319074711697</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.1911985795271106</v>
+        <v>-0.1911985796812917</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>31.80463475813573</v>
+        <v>31.80463502131448</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>28.23726838890791</v>
+        <v>28.23726827027671</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>1.678246372455477</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-1.17014678492856</v>
+        <v>-1.170146789133654</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>35.5892055010828</v>
+        <v>35.58920550985421</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>25.40986804101697</v>
+        <v>25.4098680973591</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.4960621845680346</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-3.821567966040165</v>
+        <v>-3.821567966320491</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>41.4930464919636</v>
+        <v>41.49304654736191</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>11.77303499519886</v>
+        <v>11.77303509055256</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.9405185829185964</v>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>43.41128713736712</v>
+        <v>43.41128694610934</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>26.87423962281596</v>
+        <v>26.87423986187271</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.5440602220894665</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>0.0465720404107528</v>
+        <v>0.04657204059297215</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>41.40578083171332</v>
+        <v>41.40578094143595</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>14.26415951482016</v>
+        <v>14.26415953129472</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.7367818237133354</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>-0.2500843339339102</v>
+        <v>-0.2500843338778426</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>40.60512219934121</v>
+        <v>40.60512235989697</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>20.6461827624845</v>
+        <v>20.64618274577383</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>0.5193038146236004</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>0.056685296016112</v>
+        <v>0.05668529594404398</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>41.20583795825427</v>
+        <v>41.20583796588346</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>23.47367064736804</v>
+        <v>23.47367073980674</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.3935347201005882</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-2.144610318857026</v>
+        <v>-2.14461031905328</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>313.8741780135502</v>
+        <v>313.8741780135504</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>155</v>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>40.03979126336474</v>
+        <v>40.03979133363203</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>15.1782102206773</v>
+        <v>15.17821025291175</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>1.004031322246317</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>-1.807213184977422</v>
+        <v>-1.807213185678266</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>32.67242127514922</v>
+        <v>32.67242127066007</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>24.52801480641778</v>
+        <v>24.52801484469576</v>
       </c>
       <c r="J153" s="2" t="n">
         <v>0.6060058793669049</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-3.367631158400948</v>
+        <v>-3.367631158358917</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>40.29245756917551</v>
+        <v>40.29245771605915</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>13.84638721840131</v>
+        <v>13.8463873452085</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.6277342822374155</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.2723472705389958</v>
+        <v>-0.2723472707632779</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>41.84214302158428</v>
+        <v>41.84214303281065</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>20.28628866111793</v>
+        <v>20.2862887163434</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>1.066510926519209</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.1206406580781273</v>
+        <v>-0.1206406581622256</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>305.2050768588738</v>
+        <v>305.2050768588736</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>670</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>38.9687151693331</v>
+        <v>38.96871520251771</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>21.70926503157643</v>
+        <v>21.70926515272583</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.7409943338236015</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-8.042141557348849</v>
+        <v>-8.042141559171103</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>38.47920223364049</v>
+        <v>38.47920224712615</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>19.37511152472066</v>
+        <v>19.37511152780375</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.7114175233726696</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-1.820804624287825</v>
+        <v>-1.820804624231747</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>303.461037485857</v>
+        <v>303.4610374858573</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>63.8</v>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>43.32511211465981</v>
+        <v>43.32511233008329</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>8.53992162510729</v>
+        <v>8.539921696343093</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>1.288662446083401</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>-0.04992135403540721</v>
+        <v>-0.04992135425968225</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>37.22424992718076</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>19.62863947099991</v>
+        <v>19.62863952340387</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.9453115237039595</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>-0.1652062223725366</v>
+        <v>-0.165206222442622</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>40.63629050966761</v>
+        <v>40.63629087741172</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>17.96483267782506</v>
+        <v>17.96483256674489</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.5891408943200332</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.1085403939722038</v>
+        <v>0.1085403936778476</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>41.63928100035389</v>
+        <v>41.63928131856518</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>28.49316202735302</v>
+        <v>28.4931622866813</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>1.338187363573842</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-0.09017963638581393</v>
+        <v>-0.09017963649795033</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>50.23698827936907</v>
+        <v>50.2369884270266</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>11.72633758161561</v>
+        <v>11.72633788665999</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>0.9043423997726061</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.004708546354044361</v>
+        <v>0.004708546241907592</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>29.4205079885552</v>
+        <v>29.42050803285349</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>39.33099392281549</v>
+        <v>39.33099387423464</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.6426488410063192</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>-2.325828054120265</v>
+        <v>-2.325828052998929</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>289.4339090484513</v>
+        <v>289.4339090484516</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>507</v>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>37.58037588131209</v>
+        <v>37.58037588468075</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>15.93739553750019</v>
+        <v>15.93739555534911</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.9196563424994382</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-11.25119901493813</v>
+        <v>-11.25119901507819</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>289.3470092016371</v>
+        <v>289.347009201637</v>
       </c>
       <c r="E165" s="2" t="n">
         <v>30.15</v>
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>44.70286701232482</v>
+        <v>44.70286705101589</v>
       </c>
       <c r="I165" s="2" t="n">
         <v>19.23220938709574</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.07375419677959141</v>
+        <v>-0.07375419673754215</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>284.2446359220837</v>
+        <v>284.2446359220839</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>59.2</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>42.85051880141275</v>
+        <v>42.8505187354398</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>11.13661471387521</v>
+        <v>11.13661464014776</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0.2063736436092274</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>-0.1722945710248983</v>
+        <v>-0.1722945710669563</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>284.1166161826961</v>
+        <v>284.116616182696</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>124</v>
@@ -9297,10 +9297,10 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>39.0711004518755</v>
+        <v>39.07110011207099</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>28.3753377169939</v>
+        <v>28.37533769309725</v>
       </c>
       <c r="J167" s="2" t="n">
         <v>1.508916181163134</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>-0.3644876926552238</v>
+        <v>-0.3644876920945399</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>41.87148632771403</v>
+        <v>41.87148634875773</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>15.605812903569</v>
+        <v>15.60581297803346</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.739033482556843</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-0.9425371323921022</v>
+        <v>-0.9425371325883358</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>41.23425901363784</v>
+        <v>41.23425896607601</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>12.85097660102422</v>
+        <v>12.85097677150751</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.3882725458350728</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-0.0001017772809913664</v>
+        <v>-0.0001017772669720668</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>36.6237033639153</v>
+        <v>36.62370359308563</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>14.69580599852946</v>
+        <v>14.69580608304152</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>1.313538947240605</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.06470771870021558</v>
+        <v>-0.06470771878431675</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>40.59987017755093</v>
+        <v>40.5998698686844</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>7.363215682478851</v>
+        <v>7.363215682478852</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.7648272032576218</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.01039803044754528</v>
+        <v>0.01039803058770644</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>277.5342508157362</v>
+        <v>277.5342508157364</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>10.3</v>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>43.52311509848821</v>
+        <v>43.52311515775882</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>26.19186751352709</v>
+        <v>26.19186755313946</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0.9381677593544193</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>-0.003443716802794823</v>
+        <v>-0.003443716844847566</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>46.46059921108706</v>
+        <v>46.46059944180935</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>14.23547904760391</v>
+        <v>14.23547910113962</v>
       </c>
       <c r="J173" s="2" t="n">
         <v>0.9560723796159954</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.02694780103007277</v>
+        <v>0.02694780098802266</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>274.106731070284</v>
+        <v>274.1067310702808</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>24.4</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>40.52509370207142</v>
+        <v>40.52509378380297</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>17.78936901168586</v>
+        <v>17.78936903392911</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.6188596104281092</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.1617227199160713</v>
+        <v>-0.1617227201964128</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>270.1688436402097</v>
+        <v>270.1688436402094</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>22.45</v>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>36.38947075145889</v>
+        <v>36.38947147462508</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>5.829119573848169</v>
+        <v>5.829119582062157</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.9684550499020043</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-0.05952664840975247</v>
+        <v>-0.0595266485499259</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>268.0428209179116</v>
+        <v>268.0428209179111</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>13.2</v>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>18.97506882546149</v>
+        <v>18.97506824689276</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>56.66765274163009</v>
+        <v>56.66765301664456</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>1.35546585135968</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.09159257795185105</v>
+        <v>0.09159257814809074</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>43.90896110953394</v>
+        <v>43.90896126300943</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>17.6364165177533</v>
+        <v>17.63641663159148</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.5853622963120755</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.02437902719951314</v>
+        <v>-0.02437902725557885</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>34.10734982940762</v>
+        <v>34.10734988637327</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>16.5607044598454</v>
+        <v>16.56070444632589</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>1.151863892207114</v>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>43.41313886371696</v>
+        <v>43.4131389340668</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>23.7848638959556</v>
+        <v>23.78486388245686</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>0.6460648573660819</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.2957297679478078</v>
+        <v>-0.2957297680178897</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>258.9993416577855</v>
+        <v>258.9993416577759</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>7.86</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>39.74429879875058</v>
+        <v>39.74429882373087</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>16.51420693515011</v>
+        <v>16.51420690253345</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.6674641017909009</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.0006634087450337611</v>
+        <v>-0.0006634087366242138</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>255.0750900012608</v>
+        <v>255.075090001261</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>7.01</v>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>28.25413010875415</v>
+        <v>28.25412994747734</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>21.31177682662397</v>
+        <v>21.31177673069448</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.8383153161487277</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>-0.004296269733828656</v>
+        <v>-0.004296269719811369</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>39.28922288352346</v>
+        <v>39.28922269473721</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>14.42104236910533</v>
+        <v>14.42104240185396</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>1.046525550807784</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.3295352803480049</v>
+        <v>-0.3295352789463264</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>27.21808911140265</v>
+        <v>27.2180892534012</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>15.37296160035227</v>
+        <v>15.37296169090044</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.8918768122737085</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.5434714111307044</v>
+        <v>-0.5434714123922193</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>248.4907275665884</v>
+        <v>248.4907275665888</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>91.2</v>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>36.30664328990948</v>
+        <v>36.30664331974892</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>19.54761835570364</v>
+        <v>19.54761848803551</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>0.8765172249593188</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.9495677161766582</v>
+        <v>-0.949567716709309</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>245.747764201669</v>
+        <v>245.7477642016691</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>68.5</v>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>37.57156942718464</v>
+        <v>37.57156935134058</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>11.59755053180661</v>
+        <v>11.59755058086459</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>1.201997619142229</v>
@@ -10290,7 +10290,7 @@
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>244.5096891249523</v>
+        <v>244.5096891249522</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>299</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>35.40886924565059</v>
+        <v>35.40886926893496</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>14.76245366744627</v>
+        <v>14.76245381680632</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.565533128274054</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-3.033418985476501</v>
+        <v>-3.033418986177354</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>243.9970215776541</v>
+        <v>243.9970215776542</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>0</v>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>45.67822095853519</v>
+        <v>45.6782209608545</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>11.64040724169471</v>
+        <v>11.64040726330374</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.05593945376768674</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>-0.9114449975951238</v>
+        <v>-0.9114449977392602</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>37.39972624303213</v>
+        <v>37.39972622487527</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>16.15552288408152</v>
+        <v>16.15552275789038</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>0.7317270415769943</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-16.09040186979605</v>
+        <v>-16.09040186446964</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>232.9939597222632</v>
+        <v>232.9939597222631</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>43.5</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>36.65526450368116</v>
+        <v>36.65526451209128</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>19.33693775138033</v>
+        <v>19.33693787589808</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.381099686123507</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.690956037423214</v>
+        <v>-0.6909560374792887</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>229.4520421340589</v>
+        <v>229.452042134059</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>33.6</v>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>39.64513724413143</v>
+        <v>39.64513722947932</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>19.03153236262315</v>
+        <v>19.0315323908453</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>1.499289606833824</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.01385940475740292</v>
+        <v>-0.01385940470133686</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>229.0599531549381</v>
+        <v>229.0599531549375</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>9.9</v>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>40.71721917258004</v>
+        <v>40.71721920866823</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>14.35261565097605</v>
+        <v>14.35261567107732</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>1.016587914454049</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>-0.006259320907736787</v>
+        <v>-0.006259320921753811</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>212.9700048639229</v>
+        <v>212.9700048639228</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>23.25</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>41.09699077550765</v>
+        <v>41.09699087716782</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>12.57073027523811</v>
+        <v>12.57073028760285</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.4887745902245083</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.02664916695731736</v>
+        <v>-0.0266491669713329</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>212.0640546739271</v>
+        <v>212.064054673926</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>29.6</v>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>39.869745348287</v>
+        <v>39.86974538227315</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>19.5040767090455</v>
+        <v>19.50407676961206</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.7544024772416765</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>0.006052817970153446</v>
+        <v>0.006052817900067009</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>205.1325844916776</v>
+        <v>205.1325844916775</v>
       </c>
       <c r="E194" s="2" t="n">
         <v>51</v>
@@ -10728,7 +10728,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>42.97601341425057</v>
+        <v>42.97601326651781</v>
       </c>
       <c r="I194" s="2" t="n">
         <v>13.0269215050844</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-0.009607859578649791</v>
+        <v>-0.009607859522582751</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>194.4986352386993</v>
+        <v>194.4986352386989</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>135</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>43.41537211419352</v>
+        <v>43.41537214477179</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>9.753784703875709</v>
+        <v>9.753784764184919</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>0.4874181713877122</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-1.209921010095127</v>
+        <v>-1.209921010431536</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>194.2749943462481</v>
+        <v>194.2749943462482</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>33.2</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>51.36853749311306</v>
+        <v>51.36853822983869</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>21.87750444569127</v>
+        <v>21.87750445734764</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.5368828427149932</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.2902878879251772</v>
+        <v>0.2902878875327017</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>193.994199362366</v>
+        <v>193.9941993623659</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>30.7</v>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>31.48885451695187</v>
+        <v>31.4888549905163</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>27.14364817133003</v>
+        <v>27.14364851730276</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.9041653475075144</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.1640063169623575</v>
+        <v>-0.1640063173127843</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>187.9115160297343</v>
+        <v>187.9115160297348</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>52</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>41.01119387885961</v>
+        <v>41.01119399443916</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>10.55816257709748</v>
+        <v>10.55816243453375</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>1.332110441083322</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.04266763591524048</v>
+        <v>-0.04266763602737483</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>40.77252248459436</v>
+        <v>40.77252243843732</v>
       </c>
       <c r="I200" s="2" t="n">
         <v>18.804203968253</v>
@@ -11085,7 +11085,7 @@
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>182.5495643164526</v>
+        <v>182.5495643164527</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>60.3</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>30.54493776639957</v>
+        <v>30.54493794909025</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>18.95124675026766</v>
+        <v>18.95124678257845</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>1.712478540637976</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.1984507122929149</v>
+        <v>-0.1984507126853907</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>179.4876436789487</v>
+        <v>179.4876436789486</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>33</v>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>30.77365860650808</v>
+        <v>30.77365877243633</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>25.30076628680303</v>
+        <v>25.3007663800471</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.9339999489279995</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>-0.2183579296374586</v>
+        <v>-0.2183579297776252</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>29.78694796455264</v>
+        <v>29.78694784221084</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>17.82850385424307</v>
+        <v>17.82850406670995</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.9319776067514962</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.1255569519002644</v>
+        <v>-0.1255569514236923</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>177.0147338241912</v>
+        <v>177.0147338241914</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>28.8</v>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>38.87811477252178</v>
+        <v>38.87811484477403</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>17.89207069593362</v>
+        <v>17.89207091397284</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.5571983006608549</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.2573976843153787</v>
+        <v>-0.2573976844275099</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>32.14288466492475</v>
+        <v>32.14288459008401</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>10.001571050135</v>
+        <v>10.00157106805318</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>1.251336455081089</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.337260741543761</v>
+        <v>-0.3372607413755426</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>19.64960172300412</v>
+        <v>19.64960170641554</v>
       </c>
       <c r="I206" s="2" t="n">
         <v>30.9025539486299</v>
@@ -11403,7 +11403,7 @@
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>165.7176506393257</v>
+        <v>165.7176506393259</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>69</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>24.07398587255778</v>
+        <v>24.07398609878027</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>19.23164336033934</v>
+        <v>19.23164357853424</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>2.700254546406103</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.4478388252510359</v>
+        <v>-0.4478388277741051</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>29.14329718808997</v>
+        <v>29.14329747992743</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>35.36238016032564</v>
+        <v>35.3623801252694</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>1.115437685741795</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>-0.02601769970840295</v>
+        <v>-0.02601769963831457</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>46.99000563186947</v>
+        <v>46.99000569820459</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>18.86295652290642</v>
+        <v>18.86295649045108</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.6275356325917927</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.04014534382517877</v>
+        <v>0.04014534379714479</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>159.5698175173439</v>
+        <v>159.5698175173426</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>17.9</v>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>36.70291098720343</v>
+        <v>36.70291115089715</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>14.10271013887794</v>
+        <v>14.10271003221755</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>1.50283109067795</v>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>23.36629830769334</v>
+        <v>23.36629831960214</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>16.63887793788815</v>
+        <v>16.63887797389824</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.5973835181697705</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-1.207216740545845</v>
+        <v>-1.207216741386891</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>44.29174347944276</v>
+        <v>44.29174357814254</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>16.57498851618674</v>
+        <v>16.57498848838946</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>1.114313073778932</v>
@@ -11700,7 +11700,7 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.03098193790554116</v>
+        <v>-0.03098193804571609</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>34.12301280036193</v>
+        <v>34.12301283728262</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>19.29769840997176</v>
+        <v>19.29769849472016</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.1656159786474881</v>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>39.57811602276033</v>
+        <v>39.5781161252336</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>18.00270581448142</v>
+        <v>18.00270574432291</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>0.8469336381748296</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>0.1350142116998726</v>
+        <v>0.1350142114195396</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11841,10 +11841,10 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>40.77406531491427</v>
+        <v>40.77406538819665</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>16.62272532721743</v>
+        <v>16.6227253683894</v>
       </c>
       <c r="J215" s="2" t="n">
         <v>0.9888867931416332</v>
@@ -11859,7 +11859,7 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>-0.1271844380879619</v>
+        <v>-0.1271844381019778</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>33.782589171019</v>
+        <v>33.78258926147696</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>18.0740103685713</v>
+        <v>18.07401037713882</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>1.603963970321794</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.06537947585419437</v>
+        <v>-0.06537947582615539</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>30.70588295645706</v>
+        <v>30.7058832029241</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>14.32493808450611</v>
+        <v>14.32493829268064</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.8274137709532717</v>
@@ -11986,7 +11986,7 @@
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>96.3731140496498</v>
+        <v>96.37311404964973</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>16.05</v>
@@ -12000,7 +12000,7 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>43.39718468753433</v>
+        <v>43.39718467669599</v>
       </c>
       <c r="I218" s="2" t="n">
         <v>14.03923112290522</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.07488387522135936</v>
+        <v>0.07488387524057677</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>93.74941726616755</v>
+        <v>93.74941726617789</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>22.95</v>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>35.67537594410362</v>
+        <v>35.67537582345335</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>13.94353834454118</v>
+        <v>13.94353838657988</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.7697212295967318</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.06769194177425436</v>
+        <v>-0.06769194159203151</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>84.80770226131698</v>
+        <v>84.80770226131719</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>53.5</v>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>39.5522632708687</v>
+        <v>39.55226336439601</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>18.04406406015421</v>
+        <v>18.0440640258816</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.431320706959155</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.2833578446025152</v>
+        <v>-0.2833578446866205</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12159,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>34.32202142166081</v>
+        <v>34.32202145146077</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>16.98733231958501</v>
+        <v>16.98733229979046</v>
       </c>
       <c r="J221" s="2" t="n">
         <v>0.6726405655023939</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>-0.175176639757968</v>
+        <v>-0.1751766397439506</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>83.59668369235024</v>
+        <v>83.59668369235033</v>
       </c>
       <c r="E222" s="2" t="n">
         <v>36.4</v>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>36.8891802079315</v>
+        <v>36.88918038037576</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>18.88669088840311</v>
+        <v>18.88669091303722</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>1.212801155523601</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>-0.07602743244459498</v>
+        <v>-0.07602743255672068</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v/>
       </c>
       <c r="D223" s="2" t="n">
-        <v>81.47835301545119</v>
+        <v>81.47835301545135</v>
       </c>
       <c r="E223" s="2" t="n">
         <v>30.1</v>
@@ -12265,10 +12265,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>43.54767245063795</v>
+        <v>43.54767237274702</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>9.93055481450132</v>
+        <v>9.930554857283472</v>
       </c>
       <c r="J223" s="2" t="n">
         <v>0.5676490569924377</v>
@@ -12283,7 +12283,7 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>-0.05807857833266733</v>
+        <v>-0.0580785782765969</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v/>
       </c>
       <c r="D224" s="2" t="n">
-        <v>76.67643054398958</v>
+        <v>76.67643054399031</v>
       </c>
       <c r="E224" s="2" t="n">
         <v>12.8</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>42.94993808031622</v>
+        <v>42.94993819995504</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>14.50363410182314</v>
+        <v>14.50363412528086</v>
       </c>
       <c r="J224" s="2" t="n">
         <v>0.6724353993634521</v>
@@ -12336,7 +12336,7 @@
         <v>-1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>0.01388321639176217</v>
+        <v>0.01388321632167744</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v/>
       </c>
       <c r="D225" s="2" t="n">
-        <v>66.14103780109539</v>
+        <v>66.14103780109731</v>
       </c>
       <c r="E225" s="2" t="n">
         <v>50.6</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>28.29126103033154</v>
+        <v>28.29126125340441</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>15.67624578618235</v>
+        <v>15.67624582133988</v>
       </c>
       <c r="J225" s="2" t="n">
         <v>0.6132828671121887</v>
@@ -12389,7 +12389,7 @@
         <v>-1</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>-0.263841404631266</v>
+        <v>-0.2638414053881804</v>
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v/>
       </c>
       <c r="D226" s="2" t="n">
-        <v>50.87955968601688</v>
+        <v>50.8795596860168</v>
       </c>
       <c r="E226" s="2" t="n">
         <v>9.380000000000001</v>
@@ -12424,10 +12424,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>29.50217403218842</v>
+        <v>29.50217404829901</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>18.99355976742135</v>
+        <v>18.99355986774035</v>
       </c>
       <c r="J226" s="2" t="n">
         <v>0.6960673559347924</v>
@@ -12442,7 +12442,7 @@
         <v>-1</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>-0.1524393978517128</v>
+        <v>-0.1524393979718242</v>
       </c>
       <c r="O226" s="2" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v/>
       </c>
       <c r="D227" s="2" t="n">
-        <v>49.61406940930211</v>
+        <v>49.61406940930194</v>
       </c>
       <c r="E227" s="2" t="n">
         <v>37.8</v>
@@ -12477,10 +12477,10 @@
         <v>0</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>40.1268795356326</v>
+        <v>40.12687964321095</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>7.97573017906528</v>
+        <v>7.975730310646765</v>
       </c>
       <c r="J227" s="2" t="n">
         <v>1.231777474530908</v>
@@ -12495,7 +12495,7 @@
         <v>-1</v>
       </c>
       <c r="N227" s="2" t="n">
-        <v>-0.08036340362579439</v>
+        <v>-0.08036340380801374</v>
       </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v/>
       </c>
       <c r="D228" s="2" t="n">
-        <v>42.09182382772433</v>
+        <v>42.09182382773653</v>
       </c>
       <c r="E228" s="2" t="n">
         <v>87</v>
@@ -12530,10 +12530,10 @@
         <v>0</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>33.87776184894709</v>
+        <v>33.87776310837138</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>18.47498685443718</v>
+        <v>18.47498686700787</v>
       </c>
       <c r="J228" s="2" t="n">
         <v>1.249969307849761</v>
@@ -12548,7 +12548,7 @@
         <v>-1</v>
       </c>
       <c r="N228" s="2" t="n">
-        <v>-0.347245516498341</v>
+        <v>-0.3472455171991966</v>
       </c>
       <c r="O228" s="2" t="inlineStr">
         <is>
